--- a/owlcms/src/main/resources/templates/protocol/SnCJTot-LETTER.xlsx
+++ b/owlcms/src/main/resources/templates/protocol/SnCJTot-LETTER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\protocol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3612BBFA-EF90-44A9-AA92-31858B409305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6681EB-3443-41A8-94EA-E90BFC508EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="23025" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -365,48 +365,21 @@
     <t>${t.get("Announcer")}</t>
   </si>
   <si>
-    <t>${session.announcer}</t>
-  </si>
-  <si>
-    <t>${session.marshall} ${session.marshal2}</t>
-  </si>
-  <si>
-    <t>${session.timeKeeper}</t>
-  </si>
-  <si>
-    <t>${session.technicalController} ${session.technicalController2}</t>
-  </si>
-  <si>
     <t>${t.get("Referee3")}</t>
   </si>
   <si>
     <t>${t.get("Referee1")}</t>
   </si>
   <si>
-    <t>${session.referee1}</t>
-  </si>
-  <si>
     <t>${t.get("Referee2")}</t>
   </si>
   <si>
-    <t>${session.referee2}</t>
-  </si>
-  <si>
-    <t>${session.referee3}</t>
-  </si>
-  <si>
     <t>${t.get("JuryPresident")}</t>
   </si>
   <si>
-    <t>${session.jury1}</t>
-  </si>
-  <si>
     <t>${t.get("Jury")}</t>
   </si>
   <si>
-    <t>${session.jury2} ${session.jury3} ${session.jury4} ${session.jury5}</t>
-  </si>
-  <si>
     <t>${session != null ? t.get("Group") + " :" : ""}</t>
   </si>
   <si>
@@ -417,6 +390,33 @@
   </si>
   <si>
     <t>${l.bestLifterScore}</t>
+  </si>
+  <si>
+    <t>${session.announcerAsTO} ${session.referee1AsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.marshallAsTO} ${session.marshallAsTO.federationId} ${session.marshal2AsTO} ${session.marshal2AsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.timeKeeperAsTO} ${session.timeKeeperAsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.technicalControllerAsTO} ${session.technicalControllerAsTO.federationId} ${session.technicalController2AsTO} ${session.technicalController2AsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.referee1AsTO} ${session.referee1AsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.referee2AsTO} ${session.referee2AsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.referee3AsTO} ${session.referee3AsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.jury1AsTO} ${session.jury1AsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.jury2AsTO} ${session.jury2AsTO.federationId} ${session.jury3AsTO} ${session.jury3AsTO.federationId} ${session.jury4AsTO} ${session.jury4AsTO.federationId} ${session.jury5AsTO} ${session.jury5AsTO.federationId}</t>
   </si>
 </sst>
 </file>
@@ -1112,7 +1112,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="115">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1368,35 +1368,23 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1407,6 +1395,12 @@
     <xf numFmtId="0" fontId="9" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -1415,24 +1409,32 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Accent1" xfId="1" builtinId="29" customBuiltin="1"/>
@@ -1455,15 +1457,7 @@
     <cellStyle name="Titre de la feuille" xfId="17" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2034,10 +2028,10 @@
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
       <c r="G4" s="12" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="I4"/>
       <c r="J4" s="3"/>
@@ -2047,28 +2041,28 @@
     </row>
     <row r="5" spans="1:24" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="96" t="s">
+      <c r="A6" s="109" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="96" t="s">
+      <c r="B6" s="109" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="98" t="s">
+      <c r="C6" s="111" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="100" t="s">
+      <c r="D6" s="113" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="102" t="s">
+      <c r="E6" s="105" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="102" t="s">
+      <c r="F6" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="102" t="s">
+      <c r="G6" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="102" t="s">
+      <c r="H6" s="105" t="s">
         <v>35</v>
       </c>
       <c r="I6" s="107" t="s">
@@ -2085,25 +2079,25 @@
       <c r="P6" s="108"/>
       <c r="Q6" s="108"/>
       <c r="R6" s="108"/>
-      <c r="S6" s="105" t="s">
+      <c r="S6" s="103" t="s">
         <v>39</v>
       </c>
-      <c r="T6" s="106"/>
-      <c r="U6" s="111" t="s">
-        <v>85</v>
-      </c>
-      <c r="V6" s="112"/>
+      <c r="T6" s="104"/>
+      <c r="U6" s="96" t="s">
+        <v>76</v>
+      </c>
+      <c r="V6" s="97"/>
       <c r="X6"/>
     </row>
     <row r="7" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="97"/>
-      <c r="B7" s="97"/>
-      <c r="C7" s="99"/>
-      <c r="D7" s="101"/>
-      <c r="E7" s="103"/>
-      <c r="F7" s="103"/>
-      <c r="G7" s="103"/>
-      <c r="H7" s="103"/>
+      <c r="A7" s="110"/>
+      <c r="B7" s="110"/>
+      <c r="C7" s="112"/>
+      <c r="D7" s="114"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="106"/>
+      <c r="H7" s="106"/>
       <c r="I7" s="47">
         <v>1</v>
       </c>
@@ -2140,8 +2134,8 @@
       <c r="T7" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="U7" s="113"/>
-      <c r="V7" s="114"/>
+      <c r="U7" s="98"/>
+      <c r="V7" s="99"/>
     </row>
     <row r="8" spans="1:24" s="11" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="38"/>
@@ -2244,10 +2238,10 @@
       <c r="T10" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="U10" s="109" t="s">
-        <v>86</v>
-      </c>
-      <c r="V10" s="110"/>
+      <c r="U10" s="100" t="s">
+        <v>77</v>
+      </c>
+      <c r="V10" s="101"/>
     </row>
     <row r="11" spans="1:24" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11"/>
@@ -2401,28 +2395,28 @@
         <v>68</v>
       </c>
       <c r="C17" s="84" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D17" s="85"/>
       <c r="F17" s="84" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="G17" s="85"/>
       <c r="H17" s="85"/>
       <c r="I17" s="85"/>
       <c r="L17" s="84" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="M17" s="85"/>
       <c r="N17" s="85"/>
       <c r="O17" s="85"/>
       <c r="P17" s="86"/>
       <c r="S17" s="84" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="T17" s="86"/>
       <c r="U17" s="85"/>
-      <c r="V17" s="85"/>
+      <c r="V17" s="17"/>
       <c r="W17"/>
       <c r="X17" s="85"/>
     </row>
@@ -2444,6 +2438,7 @@
       <c r="S18" s="90"/>
       <c r="T18" s="90"/>
       <c r="U18" s="90"/>
+      <c r="V18" s="115"/>
       <c r="X18" s="90"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.2">
@@ -2453,41 +2448,41 @@
       <c r="E19" s="94"/>
       <c r="F19" s="95"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="104" t="s">
-        <v>73</v>
-      </c>
-      <c r="K19" s="104"/>
+      <c r="J19" s="102" t="s">
+        <v>69</v>
+      </c>
+      <c r="K19" s="102"/>
       <c r="M19"/>
       <c r="N19" s="1"/>
       <c r="O19" s="8"/>
       <c r="T19"/>
       <c r="U19"/>
-      <c r="V19"/>
+      <c r="V19" s="116"/>
       <c r="W19"/>
       <c r="X19"/>
     </row>
     <row r="20" spans="1:24" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="83" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C20" s="84" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="D20" s="85"/>
       <c r="E20" s="83" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F20" s="84" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G20" s="85"/>
       <c r="H20" s="85"/>
       <c r="I20" s="85"/>
-      <c r="J20" s="104"/>
-      <c r="K20" s="104"/>
+      <c r="J20" s="102"/>
+      <c r="K20" s="102"/>
       <c r="L20" s="84" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="M20" s="86"/>
       <c r="N20" s="85"/>
@@ -2495,7 +2490,7 @@
       <c r="P20" s="85"/>
       <c r="T20"/>
       <c r="U20"/>
-      <c r="V20"/>
+      <c r="V20" s="116"/>
       <c r="W20"/>
       <c r="X20"/>
     </row>
@@ -2514,6 +2509,7 @@
       <c r="O21" s="90"/>
       <c r="P21" s="90"/>
       <c r="Q21" s="87"/>
+      <c r="V21" s="115"/>
       <c r="X21" s="90"/>
     </row>
     <row r="22" spans="1:24" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -2530,24 +2526,24 @@
       <c r="O22" s="8"/>
       <c r="T22"/>
       <c r="U22"/>
-      <c r="V22"/>
+      <c r="V22" s="116"/>
       <c r="W22"/>
       <c r="X22"/>
     </row>
     <row r="23" spans="1:24" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="83" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C23" s="84" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="D23" s="85"/>
       <c r="E23" s="83" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F23" s="84" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G23" s="85"/>
       <c r="H23" s="85"/>
@@ -2560,7 +2556,7 @@
       <c r="O23" s="85"/>
       <c r="T23"/>
       <c r="U23"/>
-      <c r="V23"/>
+      <c r="V23" s="116"/>
       <c r="W23"/>
       <c r="X23"/>
     </row>
@@ -2822,6 +2818,11 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="14">
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
     <mergeCell ref="U6:V7"/>
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="J19:K20"/>
@@ -2831,17 +2832,9 @@
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="I6:M6"/>
     <mergeCell ref="N6:R6"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
   </mergeCells>
   <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="2" priority="8" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="8" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2851,7 +2844,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation showErrorMessage="1" sqref="F23 F20 C20 C17 S17 L17 F17 L20 C23 H4" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation showErrorMessage="1" sqref="H4 F23 C20 C17 S17 L17 F17 F20 C23 L20" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
     <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="F10 H11:H13" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>0</formula1>
       <formula2>200</formula2>

--- a/owlcms/src/main/resources/templates/protocol/SnCJTot-LETTER.xlsx
+++ b/owlcms/src/main/resources/templates/protocol/SnCJTot-LETTER.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\protocol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6681EB-3443-41A8-94EA-E90BFC508EAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAFE967A-84E8-4EFF-8634-2383E994445A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -392,9 +392,6 @@
     <t>${l.bestLifterScore}</t>
   </si>
   <si>
-    <t>${session.announcerAsTO} ${session.referee1AsTO.federationId}</t>
-  </si>
-  <si>
     <t>${session.marshallAsTO} ${session.marshallAsTO.federationId} ${session.marshal2AsTO} ${session.marshal2AsTO.federationId}</t>
   </si>
   <si>
@@ -417,6 +414,9 @@
   </si>
   <si>
     <t>${session.jury2AsTO} ${session.jury2AsTO.federationId} ${session.jury3AsTO} ${session.jury3AsTO.federationId} ${session.jury4AsTO} ${session.jury4AsTO.federationId} ${session.jury5AsTO} ${session.jury5AsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.announcerAsTO} ${session.announcerAsTO.federationId}</t>
   </si>
 </sst>
 </file>
@@ -1368,6 +1368,38 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1395,12 +1427,6 @@
     <xf numFmtId="0" fontId="9" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -1409,32 +1435,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Accent1" xfId="1" builtinId="29" customBuiltin="1"/>
@@ -2041,63 +2041,63 @@
     </row>
     <row r="5" spans="1:24" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="109" t="s">
+      <c r="A6" s="98" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="109" t="s">
+      <c r="B6" s="98" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="111" t="s">
+      <c r="C6" s="100" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="113" t="s">
+      <c r="D6" s="102" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="105" t="s">
+      <c r="E6" s="104" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="105" t="s">
+      <c r="F6" s="104" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="105" t="s">
+      <c r="G6" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="105" t="s">
+      <c r="H6" s="104" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="107" t="s">
+      <c r="I6" s="115" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="108"/>
-      <c r="K6" s="108"/>
-      <c r="L6" s="108"/>
-      <c r="M6" s="108"/>
-      <c r="N6" s="107" t="s">
+      <c r="J6" s="116"/>
+      <c r="K6" s="116"/>
+      <c r="L6" s="116"/>
+      <c r="M6" s="116"/>
+      <c r="N6" s="115" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="108"/>
-      <c r="P6" s="108"/>
-      <c r="Q6" s="108"/>
-      <c r="R6" s="108"/>
-      <c r="S6" s="103" t="s">
+      <c r="O6" s="116"/>
+      <c r="P6" s="116"/>
+      <c r="Q6" s="116"/>
+      <c r="R6" s="116"/>
+      <c r="S6" s="113" t="s">
         <v>39</v>
       </c>
-      <c r="T6" s="104"/>
-      <c r="U6" s="96" t="s">
+      <c r="T6" s="114"/>
+      <c r="U6" s="106" t="s">
         <v>76</v>
       </c>
-      <c r="V6" s="97"/>
+      <c r="V6" s="107"/>
       <c r="X6"/>
     </row>
     <row r="7" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="110"/>
-      <c r="B7" s="110"/>
-      <c r="C7" s="112"/>
-      <c r="D7" s="114"/>
-      <c r="E7" s="106"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="106"/>
+      <c r="A7" s="99"/>
+      <c r="B7" s="99"/>
+      <c r="C7" s="101"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="105"/>
+      <c r="F7" s="105"/>
+      <c r="G7" s="105"/>
+      <c r="H7" s="105"/>
       <c r="I7" s="47">
         <v>1</v>
       </c>
@@ -2134,8 +2134,8 @@
       <c r="T7" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="U7" s="98"/>
-      <c r="V7" s="99"/>
+      <c r="U7" s="108"/>
+      <c r="V7" s="109"/>
     </row>
     <row r="8" spans="1:24" s="11" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="38"/>
@@ -2238,10 +2238,10 @@
       <c r="T10" s="59" t="s">
         <v>46</v>
       </c>
-      <c r="U10" s="100" t="s">
+      <c r="U10" s="110" t="s">
         <v>77</v>
       </c>
-      <c r="V10" s="101"/>
+      <c r="V10" s="111"/>
     </row>
     <row r="11" spans="1:24" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11"/>
@@ -2395,24 +2395,24 @@
         <v>68</v>
       </c>
       <c r="C17" s="84" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D17" s="85"/>
       <c r="F17" s="84" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G17" s="85"/>
       <c r="H17" s="85"/>
       <c r="I17" s="85"/>
       <c r="L17" s="84" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M17" s="85"/>
       <c r="N17" s="85"/>
       <c r="O17" s="85"/>
       <c r="P17" s="86"/>
       <c r="S17" s="84" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="T17" s="86"/>
       <c r="U17" s="85"/>
@@ -2438,7 +2438,7 @@
       <c r="S18" s="90"/>
       <c r="T18" s="90"/>
       <c r="U18" s="90"/>
-      <c r="V18" s="115"/>
+      <c r="V18" s="96"/>
       <c r="X18" s="90"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.2">
@@ -2448,16 +2448,16 @@
       <c r="E19" s="94"/>
       <c r="F19" s="95"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="102" t="s">
+      <c r="J19" s="112" t="s">
         <v>69</v>
       </c>
-      <c r="K19" s="102"/>
+      <c r="K19" s="112"/>
       <c r="M19"/>
       <c r="N19" s="1"/>
       <c r="O19" s="8"/>
       <c r="T19"/>
       <c r="U19"/>
-      <c r="V19" s="116"/>
+      <c r="V19" s="97"/>
       <c r="W19"/>
       <c r="X19"/>
     </row>
@@ -2467,22 +2467,22 @@
         <v>70</v>
       </c>
       <c r="C20" s="84" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D20" s="85"/>
       <c r="E20" s="83" t="s">
         <v>71</v>
       </c>
       <c r="F20" s="84" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G20" s="85"/>
       <c r="H20" s="85"/>
       <c r="I20" s="85"/>
-      <c r="J20" s="102"/>
-      <c r="K20" s="102"/>
+      <c r="J20" s="112"/>
+      <c r="K20" s="112"/>
       <c r="L20" s="84" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M20" s="86"/>
       <c r="N20" s="85"/>
@@ -2490,7 +2490,7 @@
       <c r="P20" s="85"/>
       <c r="T20"/>
       <c r="U20"/>
-      <c r="V20" s="116"/>
+      <c r="V20" s="97"/>
       <c r="W20"/>
       <c r="X20"/>
     </row>
@@ -2509,7 +2509,7 @@
       <c r="O21" s="90"/>
       <c r="P21" s="90"/>
       <c r="Q21" s="87"/>
-      <c r="V21" s="115"/>
+      <c r="V21" s="96"/>
       <c r="X21" s="90"/>
     </row>
     <row r="22" spans="1:24" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
@@ -2526,7 +2526,7 @@
       <c r="O22" s="8"/>
       <c r="T22"/>
       <c r="U22"/>
-      <c r="V22" s="116"/>
+      <c r="V22" s="97"/>
       <c r="W22"/>
       <c r="X22"/>
     </row>
@@ -2536,14 +2536,14 @@
         <v>72</v>
       </c>
       <c r="C23" s="84" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D23" s="85"/>
       <c r="E23" s="83" t="s">
         <v>73</v>
       </c>
       <c r="F23" s="84" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G23" s="85"/>
       <c r="H23" s="85"/>
@@ -2556,7 +2556,7 @@
       <c r="O23" s="85"/>
       <c r="T23"/>
       <c r="U23"/>
-      <c r="V23" s="116"/>
+      <c r="V23" s="97"/>
       <c r="W23"/>
       <c r="X23"/>
     </row>
@@ -2818,11 +2818,6 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="14">
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
     <mergeCell ref="U6:V7"/>
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="J19:K20"/>
@@ -2832,6 +2827,11 @@
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="I6:M6"/>
     <mergeCell ref="N6:R6"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
   </mergeCells>
   <conditionalFormatting sqref="D8">
     <cfRule type="expression" dxfId="1" priority="8" stopIfTrue="1">

--- a/owlcms/src/main/resources/templates/protocol/SnCJTot-LETTER.xlsx
+++ b/owlcms/src/main/resources/templates/protocol/SnCJTot-LETTER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\protocol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAFE967A-84E8-4EFF-8634-2383E994445A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6EC30F3-0197-40D2-8F68-F7920B6AFE0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2400" yWindow="7425" windowWidth="24615" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -25,21 +25,21 @@
     <definedName name="CategoryFilter">Results!#REF!</definedName>
     <definedName name="CLUB">Results!#REF!</definedName>
     <definedName name="Collet">#REF!</definedName>
-    <definedName name="_xlnm.Criteria" localSheetId="0">Results!$A$1:$CF$82</definedName>
+    <definedName name="_xlnm.Criteria" localSheetId="0">Results!$A$1:$CF$99</definedName>
     <definedName name="demandé">Results!#REF!</definedName>
     <definedName name="dernier">Results!#REF!</definedName>
     <definedName name="essais">Results!#REF!</definedName>
     <definedName name="essaisArr">Results!#REF!</definedName>
     <definedName name="Excel_BuiltIn_Criteria_1">Results!#REF!</definedName>
-    <definedName name="GroupeCourant">Results!$H$4</definedName>
+    <definedName name="GroupeCourant">Results!$K$4</definedName>
     <definedName name="Groupes">#REF!</definedName>
     <definedName name="GroupFilter">Results!#REF!</definedName>
     <definedName name="InactiveGroupFilter">Results!#REF!</definedName>
     <definedName name="isSnatch">Results!#REF!</definedName>
     <definedName name="lbParKg">Results!#REF!</definedName>
-    <definedName name="LignesCalculs">Results!#REF!</definedName>
+    <definedName name="LignesCalculs">Results!$25:$25</definedName>
     <definedName name="LignesEntête">Results!$1:$5</definedName>
-    <definedName name="LignesOfficiels">Results!$12:$15</definedName>
+    <definedName name="LignesOfficiels">Results!$17:$24</definedName>
     <definedName name="M_F">Results!#REF!</definedName>
     <definedName name="NAIS.">Results!#REF!</definedName>
     <definedName name="NbCollet">#REF!</definedName>
@@ -55,12 +55,14 @@
     <definedName name="TAS">Results!#REF!</definedName>
     <definedName name="tirage">Results!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="181029" iterate="1"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -74,80 +76,68 @@
     <author>Jean-François Lamy</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{CBD6DE4D-1C2E-4747-83CB-FDC2A1E37FF6}">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{5464D8D0-CD5E-425C-A581-A77008842DB5}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>jx:area(lastCell="V23")</t>
         </r>
       </text>
     </comment>
-    <comment ref="A8" authorId="0" shapeId="0" xr:uid="{78C9474A-E803-416B-8110-C82A4ADE45B0}">
+    <comment ref="A8" authorId="0" shapeId="0" xr:uid="{CEBD2170-0D1A-40A3-B9D6-62E3599ECF09}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>jx:each(items="athletes" var="group" groupBy="group.categorySortCode" groupOrder="ASC" lastCell="V10")</t>
         </r>
       </text>
     </comment>
-    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{8CC34236-0149-42F9-B1CC-CCB1421EA3C0}">
+    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{F0A7DC28-4FBA-4A0F-B1F3-C337DC82D113}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
-          <t xml:space="preserve">jx:each(items="group.items" var="l"  varIndex="lifterLoop" lastCell="V10")
-</t>
+          <t>jx:each(items="group.items" var="l"  varIndex="lifterLoop" lastCell="V10")</t>
         </r>
       </text>
     </comment>
-    <comment ref="A12" authorId="0" shapeId="0" xr:uid="{4F1B1DD0-0511-44CE-9AD5-6D11674303E8}">
+    <comment ref="A12" authorId="0" shapeId="0" xr:uid="{970BB391-BC34-4352-A877-A2663ADBC3A4}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>jx:if(condition="records != null" lastCell="V15")</t>
         </r>
       </text>
     </comment>
-    <comment ref="A15" authorId="0" shapeId="0" xr:uid="{2E0ABA1D-29D1-409E-8171-6D58FBB63FC3}">
+    <comment ref="A15" authorId="0" shapeId="0" xr:uid="{1E324CE8-95D7-4732-87D4-D0D1EB5131F4}">
       <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Jean-François Lamy:</t>
-        </r>
         <r>
           <rPr>
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
-          <t xml:space="preserve">
-jx:each(items="records" var="r" lastCell="V15")</t>
+          <t>jx:each(items="records" var="r" lastCell="V15")</t>
         </r>
       </text>
     </comment>
@@ -156,7 +146,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="93">
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
   <si>
     <t>${l.lotNumber}</t>
   </si>
@@ -230,6 +223,9 @@
     <t>${competition.federationEMail}</t>
   </si>
   <si>
+    <t>${l.startNumber}</t>
+  </si>
+  <si>
     <t>${l.formattedBirth}</t>
   </si>
   <si>
@@ -275,109 +271,121 @@
     <t>${t.get("Results.Membership")}</t>
   </si>
   <si>
+    <t>${t.get("Results.Start")}</t>
+  </si>
+  <si>
+    <t>${t.get("Results.Lot")}</t>
+  </si>
+  <si>
+    <t>${t.get("Results.Best")}</t>
+  </si>
+  <si>
+    <t>${t.get("Results.Snatch_abbrev")}</t>
+  </si>
+  <si>
     <t>${t.get("Results.Total")}</t>
   </si>
   <si>
     <t>${t.get("Results.Rank")}</t>
   </si>
   <si>
+    <t>${t.get("Announcer")}</t>
+  </si>
+  <si>
+    <t>${t.get("Marshall")}</t>
+  </si>
+  <si>
+    <t>${t.get("Timekeeper")}</t>
+  </si>
+  <si>
+    <t>${t.get("Results.Controller")}</t>
+  </si>
+  <si>
+    <t>${t.get("Referee1")}</t>
+  </si>
+  <si>
+    <t>${t.get("Referee2")}</t>
+  </si>
+  <si>
+    <t>${t.get("Referee3")}</t>
+  </si>
+  <si>
+    <t>${t.get("Jury")}</t>
+  </si>
+  <si>
+    <t>${t.get("Results.CJ_abbrev")}</t>
+  </si>
+  <si>
+    <t>${group.item.category}</t>
+  </si>
+  <si>
     <t>${competition.localizedCompetitionDate}</t>
   </si>
   <si>
-    <t>${t.get("Lot")}</t>
-  </si>
-  <si>
-    <t>${t.get("Results.max")}</t>
-  </si>
-  <si>
-    <t>${l.snatchRank}</t>
-  </si>
-  <si>
-    <t>${l.cleanJerkRank}</t>
-  </si>
-  <si>
-    <t>${l.totalRank}</t>
-  </si>
-  <si>
-    <t>${group.item.displayCategory}</t>
+    <t>${r.recordFederation}</t>
+  </si>
+  <si>
+    <t>${r.recordName}</t>
+  </si>
+  <si>
+    <t>${r.recordValue}</t>
+  </si>
+  <si>
+    <t>${r.nation}</t>
+  </si>
+  <si>
+    <t>${r.recordDateAsString}</t>
+  </si>
+  <si>
+    <t>${r.groupNameString}</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ${r.birth}</t>
   </si>
   <si>
     <t>${t.get("Preparation.Records")}</t>
   </si>
   <si>
+    <t>${t.get("Group")}</t>
+  </si>
+  <si>
+    <t>${t.get("Name")}</t>
+  </si>
+  <si>
+    <t>${t.get("Results.RecordName")}</t>
+  </si>
+  <si>
+    <t>${t.get("Results.RecordWeight")}</t>
+  </si>
+  <si>
+    <t>${t.get("Results.RecordDate")}</t>
+  </si>
+  <si>
+    <t>${t.get("JuryPresident")}</t>
+  </si>
+  <si>
+    <t>${t.get("Results.RecordAgeGroup")}</t>
+  </si>
+  <si>
     <t>${t.get("Results.RecordFederation")}</t>
   </si>
   <si>
-    <t>${t.get("Results.RecordName")}</t>
-  </si>
-  <si>
-    <t>${t.get("Results.RecordAgeGroup")}</t>
-  </si>
-  <si>
     <t>${t.get("Results.RecordKind")}</t>
   </si>
   <si>
-    <t>${t.get("Results.RecordWeight")}</t>
-  </si>
-  <si>
-    <t>${t.get("Name")}</t>
-  </si>
-  <si>
-    <t>${t.get("Group")}</t>
-  </si>
-  <si>
-    <t>${t.get("Results.RecordDate")}</t>
-  </si>
-  <si>
-    <t>${r.recordFederation}</t>
-  </si>
-  <si>
-    <t>${r.recordName}</t>
-  </si>
-  <si>
-    <t>${r.recordValue}</t>
-  </si>
-  <si>
-    <t>${r.nation}</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ${r.birth}</t>
-  </si>
-  <si>
-    <t>${r.groupNameString}</t>
-  </si>
-  <si>
-    <t>${r.recordDateAsString}</t>
+    <t>${r.bwCatString}</t>
   </si>
   <si>
     <t>${r.ageGrp} ${r.gender}</t>
   </si>
   <si>
-    <t>${r.bwCatString}</t>
-  </si>
-  <si>
     <t>${r.resAthleteName}</t>
   </si>
   <si>
     <t>${r.resRecordLift}</t>
   </si>
   <si>
-    <t>${t.get("Announcer")}</t>
-  </si>
-  <si>
-    <t>${t.get("Referee3")}</t>
-  </si>
-  <si>
-    <t>${t.get("Referee1")}</t>
-  </si>
-  <si>
-    <t>${t.get("Referee2")}</t>
-  </si>
-  <si>
-    <t>${t.get("JuryPresident")}</t>
-  </si>
-  <si>
-    <t>${t.get("Jury")}</t>
+    <t>${l.totalRank &lt; 0 ? "inv." : (l.totalRank &gt; 0 ? l.totalRank : "" )}</t>
   </si>
   <si>
     <t>${session != null ? t.get("Group") + " :" : ""}</t>
@@ -392,6 +400,15 @@
     <t>${l.bestLifterScore}</t>
   </si>
   <si>
+    <t>${session.referee1AsTO} ${session.referee1AsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.referee2AsTO} ${session.referee2AsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.referee3AsTO} ${session.referee3AsTO.federationId}</t>
+  </si>
+  <si>
     <t>${session.marshallAsTO} ${session.marshallAsTO.federationId} ${session.marshal2AsTO} ${session.marshal2AsTO.federationId}</t>
   </si>
   <si>
@@ -399,15 +416,6 @@
   </si>
   <si>
     <t>${session.technicalControllerAsTO} ${session.technicalControllerAsTO.federationId} ${session.technicalController2AsTO} ${session.technicalController2AsTO.federationId}</t>
-  </si>
-  <si>
-    <t>${session.referee1AsTO} ${session.referee1AsTO.federationId}</t>
-  </si>
-  <si>
-    <t>${session.referee2AsTO} ${session.referee2AsTO.federationId}</t>
-  </si>
-  <si>
-    <t>${session.referee3AsTO} ${session.referee3AsTO.federationId}</t>
   </si>
   <si>
     <t>${session.jury1AsTO} ${session.jury1AsTO.federationId}</t>
@@ -423,12 +431,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_-#,##0;[Red]\(#,##0\);\-"/>
-    <numFmt numFmtId="165" formatCode="0;\(0\);\-"/>
-    <numFmt numFmtId="166" formatCode="0.000;;\-"/>
+  <numFmts count="6">
+    <numFmt numFmtId="164" formatCode="0.0;;"/>
+    <numFmt numFmtId="165" formatCode="_ * #,##0_)\ _$_ ;_ * \(#,##0&quot;) &quot;_$_ ;_ * \-??_)\ _$_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_-#,##0;[Red]\(#,##0\);\-"/>
+    <numFmt numFmtId="167" formatCode="0;\(0\);\-"/>
+    <numFmt numFmtId="168" formatCode="0.000;;\-"/>
+    <numFmt numFmtId="169" formatCode="0;\-;\-"/>
   </numFmts>
-  <fonts count="35" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -510,6 +521,18 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="7"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -557,18 +580,6 @@
     <font>
       <sz val="10"/>
       <color indexed="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -593,12 +604,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -622,29 +627,16 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="7"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="15">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -712,12 +704,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="9"/>
-        <bgColor indexed="26"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="31"/>
       </patternFill>
@@ -729,7 +715,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -775,14 +761,29 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
       <right/>
       <top style="thin">
         <color indexed="8"/>
@@ -793,40 +794,9 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -841,78 +811,7 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
       <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -928,41 +827,17 @@
       <top style="thin">
         <color indexed="8"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color indexed="8"/>
       </left>
-      <right/>
-      <top style="thin">
+      <right style="thin">
         <color indexed="8"/>
-      </top>
+      </right>
+      <top/>
       <bottom style="thin">
         <color indexed="8"/>
       </bottom>
@@ -982,11 +857,81 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
         <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
@@ -995,11 +940,9 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="thin">
-        <color indexed="8"/>
+        <color indexed="64"/>
       </right>
       <top/>
       <bottom style="thin">
@@ -1012,7 +955,7 @@
         <color indexed="8"/>
       </left>
       <right style="thin">
-        <color indexed="8"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
@@ -1024,18 +967,9 @@
       <left style="thin">
         <color indexed="8"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -1104,7 +1038,7 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1112,7 +1046,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1123,9 +1057,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1133,29 +1064,130 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="1" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1163,33 +1195,20 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="1" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1198,242 +1217,171 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="12" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="12" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="12" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="12" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="14" xfId="12" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="12" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="15" fillId="0" borderId="15" xfId="12" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="22" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="20" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="23" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="12" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="12" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="12" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="12" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="9" xfId="12" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="19">
@@ -1457,7 +1405,15 @@
     <cellStyle name="Titre de la feuille" xfId="17" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="34"/>
+          <bgColor indexed="13"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1906,17 +1862,17 @@
   <sheetPr codeName="Feuil4">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X108"/>
+  <dimension ref="A1:X125"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="1"/>
     <col min="2" max="2" width="5.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="27.28515625" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.28515625" customWidth="1"/>
     <col min="6" max="6" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.28515625" style="2" customWidth="1"/>
     <col min="10" max="10" width="10.42578125" style="1" customWidth="1"/>
     <col min="11" max="13" width="7.7109375" style="1" customWidth="1"/>
@@ -1925,323 +1881,313 @@
     <col min="16" max="18" width="7.7109375" style="1" customWidth="1"/>
     <col min="19" max="19" width="7.7109375" customWidth="1"/>
     <col min="20" max="20" width="8.42578125" style="1" customWidth="1"/>
-    <col min="21" max="22" width="7" style="1" customWidth="1"/>
+    <col min="21" max="21" width="7" style="1" customWidth="1"/>
+    <col min="22" max="22" width="7" style="3" customWidth="1"/>
     <col min="23" max="23" width="10.140625" style="1" customWidth="1"/>
     <col min="24" max="24" width="8.140625" style="1" hidden="1" customWidth="1"/>
     <col min="25" max="25" width="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="49" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="15"/>
+      <c r="J1" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+    </row>
+    <row r="2" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="53" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="54"/>
+      <c r="C2" s="4"/>
+      <c r="J2" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="99"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="57"/>
+      <c r="Q2" s="58"/>
+      <c r="R2" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="S2" t="s">
+        <v>18</v>
+      </c>
+      <c r="T2" s="58"/>
+      <c r="U2" s="58"/>
+    </row>
+    <row r="3" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="59" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="60"/>
+      <c r="J3" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="120" t="s">
+        <v>57</v>
+      </c>
+      <c r="L3" s="120"/>
+      <c r="M3" s="120"/>
+      <c r="N3" s="120"/>
+      <c r="O3" s="120"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="61"/>
+      <c r="R3" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" s="16"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="18"/>
-      <c r="M1" s="18"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="18"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="S1" s="19"/>
-      <c r="T1" s="19"/>
-      <c r="U1" s="19"/>
-      <c r="V1" s="19"/>
-    </row>
-    <row r="2" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="5"/>
-      <c r="G2" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="23"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="18"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="1"/>
-    </row>
-    <row r="3" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="31"/>
-      <c r="G3" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="45" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="32"/>
-      <c r="O3" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q3" s="34"/>
-      <c r="R3" s="34"/>
-      <c r="S3" s="35"/>
-      <c r="T3" s="35"/>
-      <c r="U3" s="35"/>
-      <c r="V3" s="35"/>
+      <c r="T3" s="63"/>
+      <c r="U3" s="63"/>
+      <c r="V3" s="96"/>
     </row>
     <row r="4" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="G4" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="H4" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="I4"/>
-      <c r="J4" s="3"/>
-      <c r="O4" s="12"/>
-      <c r="P4" s="36"/>
-      <c r="S4" s="1"/>
+      <c r="A4" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="59"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="J4" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="K4" s="100" t="s">
+        <v>81</v>
+      </c>
+      <c r="L4"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="Q4"/>
+      <c r="R4" s="32"/>
+      <c r="S4" s="64"/>
     </row>
     <row r="5" spans="1:24" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="98" t="s">
+      <c r="A6" s="7"/>
+      <c r="C6" s="8"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="109" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="98" t="s">
+      <c r="L6" s="110"/>
+      <c r="M6" s="111"/>
+      <c r="N6" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="O6" s="109" t="s">
+        <v>39</v>
+      </c>
+      <c r="P6" s="110"/>
+      <c r="Q6" s="111"/>
+      <c r="R6" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="S6" s="106" t="s">
+        <v>45</v>
+      </c>
+      <c r="T6" s="104" t="s">
+        <v>46</v>
+      </c>
+      <c r="U6" s="112" t="s">
+        <v>82</v>
+      </c>
+      <c r="V6" s="113"/>
+      <c r="X6"/>
+    </row>
+    <row r="7" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="100" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="102" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="104" t="s">
+      <c r="D7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="104" t="s">
+      <c r="E7" s="109" t="s">
         <v>33</v>
       </c>
-      <c r="G6" s="104" t="s">
+      <c r="F7" s="111"/>
+      <c r="G7" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="H6" s="104" t="s">
+      <c r="H7" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I6" s="115" t="s">
+      <c r="I7" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="116"/>
-      <c r="K6" s="116"/>
-      <c r="L6" s="116"/>
-      <c r="M6" s="116"/>
-      <c r="N6" s="115" t="s">
+      <c r="J7" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="116"/>
-      <c r="P6" s="116"/>
-      <c r="Q6" s="116"/>
-      <c r="R6" s="116"/>
-      <c r="S6" s="113" t="s">
-        <v>39</v>
-      </c>
-      <c r="T6" s="114"/>
-      <c r="U6" s="106" t="s">
-        <v>76</v>
-      </c>
-      <c r="V6" s="107"/>
-      <c r="X6"/>
-    </row>
-    <row r="7" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="99"/>
-      <c r="B7" s="99"/>
-      <c r="C7" s="101"/>
-      <c r="D7" s="103"/>
-      <c r="E7" s="105"/>
-      <c r="F7" s="105"/>
-      <c r="G7" s="105"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="47">
+      <c r="K7" s="10">
         <v>1</v>
       </c>
-      <c r="J7" s="46">
+      <c r="L7" s="10">
         <v>2</v>
       </c>
-      <c r="K7" s="46">
+      <c r="M7" s="10">
         <v>3</v>
       </c>
-      <c r="L7" s="48" t="s">
-        <v>43</v>
-      </c>
-      <c r="M7" s="49" t="s">
-        <v>40</v>
-      </c>
-      <c r="N7" s="46">
+      <c r="N7" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="O7" s="10">
         <v>1</v>
       </c>
-      <c r="O7" s="46">
+      <c r="P7" s="10">
         <v>2</v>
       </c>
-      <c r="P7" s="46">
+      <c r="Q7" s="10">
         <v>3</v>
       </c>
-      <c r="Q7" s="48" t="s">
-        <v>43</v>
-      </c>
-      <c r="R7" s="49" t="s">
-        <v>40</v>
-      </c>
-      <c r="S7" s="50" t="s">
-        <v>39</v>
-      </c>
-      <c r="T7" s="49" t="s">
-        <v>40</v>
-      </c>
-      <c r="U7" s="108"/>
-      <c r="V7" s="109"/>
-    </row>
-    <row r="8" spans="1:24" s="11" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="38"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="40"/>
+      <c r="R7" s="45" t="s">
+        <v>55</v>
+      </c>
+      <c r="S7" s="107"/>
+      <c r="T7" s="105"/>
+      <c r="U7" s="114"/>
+      <c r="V7" s="115"/>
+    </row>
+    <row r="8" spans="1:24" s="28" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="68"/>
+      <c r="B8" s="68"/>
+      <c r="C8" s="68"/>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="70"/>
     </row>
     <row r="9" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="41" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="60"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="43"/>
-      <c r="K9" s="43"/>
-      <c r="L9" s="43"/>
-      <c r="M9" s="43"/>
-      <c r="N9" s="43"/>
-      <c r="O9" s="43"/>
-      <c r="P9" s="43"/>
-      <c r="Q9" s="43"/>
-      <c r="R9" s="43"/>
-      <c r="S9" s="43"/>
-      <c r="T9" s="43"/>
-      <c r="U9" s="43"/>
-      <c r="V9" s="44"/>
+      <c r="A9" s="71" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="72"/>
+      <c r="C9" s="73"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="73"/>
+      <c r="F9" s="73"/>
+      <c r="G9" s="73"/>
+      <c r="H9" s="73"/>
+      <c r="I9" s="73"/>
+      <c r="J9" s="73"/>
+      <c r="K9" s="73"/>
+      <c r="L9" s="73"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="73"/>
+      <c r="O9" s="73"/>
+      <c r="P9" s="73"/>
+      <c r="Q9" s="73"/>
+      <c r="R9" s="73"/>
+      <c r="S9" s="73"/>
+      <c r="T9" s="73"/>
+      <c r="U9" s="73"/>
+      <c r="V9" s="101"/>
       <c r="X9"/>
     </row>
-    <row r="10" spans="1:24" s="11" customFormat="1" ht="21.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="9" t="s">
+    <row r="10" spans="1:24" s="28" customFormat="1" ht="21.2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="52" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="52" t="s">
+      <c r="D10" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="53" t="s">
+      <c r="E10" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="54" t="s">
+      <c r="F10" s="119"/>
+      <c r="G10" s="66" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="J10" s="65" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="M10" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="N10" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="O10" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="P10" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="G10" s="53" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="55" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" s="10" t="s">
+      <c r="R10" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="J10" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="K10" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="L10" s="56" t="s">
+      <c r="S10" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="M10" s="57" t="s">
-        <v>44</v>
-      </c>
-      <c r="N10" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="O10" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="P10" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q10" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="R10" s="57" t="s">
-        <v>45</v>
-      </c>
-      <c r="S10" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="T10" s="59" t="s">
-        <v>46</v>
-      </c>
-      <c r="U10" s="110" t="s">
-        <v>77</v>
-      </c>
-      <c r="V10" s="111"/>
+      <c r="T10" s="46" t="s">
+        <v>79</v>
+      </c>
+      <c r="U10" s="116" t="s">
+        <v>83</v>
+      </c>
+      <c r="V10" s="117"/>
     </row>
     <row r="11" spans="1:24" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11"/>
@@ -2261,200 +2207,231 @@
       <c r="W11"/>
       <c r="X11"/>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+    <row r="12" spans="1:24" s="49" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="J12" s="50"/>
+    </row>
+    <row r="13" spans="1:24" s="49" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="75"/>
+      <c r="B13" s="75"/>
+      <c r="C13" s="75"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="75"/>
+      <c r="F13" s="75"/>
+      <c r="G13" s="75"/>
+      <c r="H13" s="75"/>
+      <c r="I13" s="75"/>
+      <c r="J13" s="81"/>
+      <c r="K13" s="75"/>
+      <c r="L13" s="75"/>
+      <c r="M13" s="75"/>
+      <c r="N13" s="75"/>
+      <c r="O13" s="75"/>
+      <c r="P13" s="81"/>
+      <c r="Q13" s="81"/>
+      <c r="R13" s="81"/>
+      <c r="S13" s="75"/>
+      <c r="T13" s="75"/>
+      <c r="U13" s="81"/>
+      <c r="V13" s="81"/>
+    </row>
+    <row r="14" spans="1:24" s="93" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A14" s="84" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="85"/>
+      <c r="C14" s="86"/>
+      <c r="D14" s="87" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="88" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" s="87" t="s">
+        <v>34</v>
+      </c>
+      <c r="G14" s="89" t="s">
+        <v>74</v>
+      </c>
+      <c r="H14" s="90"/>
+      <c r="I14" s="87" t="s">
+        <v>69</v>
+      </c>
+      <c r="J14" s="84" t="s">
+        <v>67</v>
+      </c>
+      <c r="K14" s="91"/>
+      <c r="L14" s="85"/>
+      <c r="M14" s="86"/>
+      <c r="N14" s="84" t="s">
+        <v>36</v>
+      </c>
+      <c r="O14" s="85"/>
+      <c r="P14" s="92"/>
+      <c r="Q14" s="84" t="s">
+        <v>37</v>
+      </c>
+      <c r="R14" s="85"/>
+      <c r="S14" s="84" t="s">
+        <v>66</v>
+      </c>
+      <c r="T14" s="91"/>
+      <c r="U14" s="84" t="s">
+        <v>70</v>
+      </c>
+      <c r="V14" s="92"/>
+      <c r="X14" s="86"/>
+    </row>
+    <row r="15" spans="1:24" s="74" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="76" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="77"/>
+      <c r="C15" s="78"/>
+      <c r="D15" s="79" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="80" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="95" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15" s="80" t="s">
+        <v>78</v>
+      </c>
+      <c r="H15" s="78"/>
+      <c r="I15" s="94" t="s">
+        <v>60</v>
+      </c>
+      <c r="J15" s="80" t="s">
+        <v>77</v>
+      </c>
+      <c r="K15" s="77"/>
+      <c r="L15" s="77"/>
+      <c r="M15" s="78"/>
+      <c r="N15" s="80" t="s">
+        <v>61</v>
+      </c>
+      <c r="O15" s="77"/>
+      <c r="P15" s="78"/>
+      <c r="Q15" s="76" t="s">
+        <v>64</v>
+      </c>
+      <c r="R15" s="77"/>
+      <c r="S15" s="83" t="s">
+        <v>63</v>
+      </c>
+      <c r="T15" s="77"/>
+      <c r="U15" s="82" t="s">
+        <v>62</v>
+      </c>
+      <c r="V15" s="78"/>
+      <c r="X15" s="78"/>
+    </row>
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="121" t="s">
         <v>48</v>
       </c>
-      <c r="J12" s="15"/>
-    </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="61"/>
-      <c r="B13" s="61"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61"/>
-      <c r="J13" s="62"/>
-      <c r="K13" s="61"/>
-      <c r="L13" s="61"/>
-      <c r="M13" s="61"/>
-      <c r="N13" s="61"/>
-      <c r="O13" s="61"/>
-      <c r="P13" s="62"/>
-      <c r="Q13" s="62"/>
-      <c r="R13" s="62"/>
-      <c r="S13" s="61"/>
-      <c r="T13" s="61"/>
-      <c r="U13" s="62"/>
-      <c r="V13" s="62"/>
-    </row>
-    <row r="14" spans="1:24" s="72" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A14" s="63" t="s">
+      <c r="G16" s="24"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="103" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="64"/>
-      <c r="C14" s="65"/>
-      <c r="D14" s="66" t="s">
+      <c r="K16" s="103"/>
+      <c r="L16" s="14"/>
+      <c r="N16" s="16"/>
+      <c r="P16" s="14"/>
+      <c r="Q16" s="108" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="67" t="s">
-        <v>51</v>
-      </c>
-      <c r="F14" s="66" t="s">
-        <v>32</v>
-      </c>
-      <c r="G14" s="68" t="s">
-        <v>52</v>
-      </c>
-      <c r="H14" s="69"/>
-      <c r="I14" s="66" t="s">
-        <v>53</v>
-      </c>
-      <c r="J14" s="63" t="s">
-        <v>54</v>
-      </c>
-      <c r="K14" s="70"/>
-      <c r="L14" s="64"/>
-      <c r="M14" s="65"/>
-      <c r="N14" s="63" t="s">
-        <v>34</v>
-      </c>
-      <c r="O14" s="64"/>
-      <c r="P14" s="71"/>
-      <c r="Q14" s="63" t="s">
-        <v>35</v>
-      </c>
-      <c r="R14" s="64"/>
-      <c r="S14" s="63" t="s">
-        <v>55</v>
-      </c>
-      <c r="T14" s="70"/>
-      <c r="U14" s="63" t="s">
-        <v>56</v>
-      </c>
-      <c r="V14" s="71"/>
-      <c r="X14" s="65"/>
-    </row>
-    <row r="15" spans="1:24" s="80" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="73" t="s">
-        <v>57</v>
-      </c>
-      <c r="B15" s="74"/>
-      <c r="C15" s="75"/>
-      <c r="D15" s="76" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" s="77" t="s">
-        <v>64</v>
-      </c>
-      <c r="F15" s="82" t="s">
-        <v>65</v>
-      </c>
-      <c r="G15" s="77" t="s">
-        <v>67</v>
-      </c>
-      <c r="H15" s="75"/>
-      <c r="I15" s="81" t="s">
-        <v>59</v>
-      </c>
-      <c r="J15" s="77" t="s">
-        <v>66</v>
-      </c>
-      <c r="K15" s="74"/>
-      <c r="L15" s="74"/>
-      <c r="M15" s="75"/>
-      <c r="N15" s="77" t="s">
-        <v>60</v>
-      </c>
-      <c r="O15" s="74"/>
-      <c r="P15" s="75"/>
-      <c r="Q15" s="73" t="s">
-        <v>61</v>
-      </c>
-      <c r="R15" s="74"/>
-      <c r="S15" s="78" t="s">
-        <v>62</v>
-      </c>
-      <c r="T15" s="74"/>
-      <c r="U15" s="79" t="s">
-        <v>63</v>
-      </c>
-      <c r="V15" s="75"/>
-      <c r="X15" s="75"/>
-    </row>
-    <row r="16" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F16" s="1"/>
-      <c r="U16" s="8"/>
+      <c r="R16" s="108"/>
+      <c r="S16" s="47"/>
+      <c r="T16" s="14"/>
+      <c r="U16" s="12"/>
+      <c r="V16" s="16"/>
+      <c r="W16" s="14"/>
+      <c r="X16" s="14" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
-      <c r="B17" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="84" t="s">
-        <v>86</v>
-      </c>
-      <c r="D17" s="85"/>
-      <c r="F17" s="84" t="s">
-        <v>78</v>
-      </c>
-      <c r="G17" s="85"/>
-      <c r="H17" s="85"/>
-      <c r="I17" s="85"/>
-      <c r="L17" s="84" t="s">
-        <v>79</v>
-      </c>
-      <c r="M17" s="85"/>
-      <c r="N17" s="85"/>
-      <c r="O17" s="85"/>
-      <c r="P17" s="86"/>
-      <c r="S17" s="84" t="s">
-        <v>80</v>
-      </c>
-      <c r="T17" s="86"/>
-      <c r="U17" s="85"/>
-      <c r="V17" s="17"/>
+      <c r="B17" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" s="17"/>
+      <c r="E17" s="121"/>
+      <c r="F17" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="103"/>
+      <c r="K17" s="103"/>
+      <c r="L17" s="41" t="s">
+        <v>88</v>
+      </c>
+      <c r="M17" s="17"/>
+      <c r="N17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="19"/>
+      <c r="Q17" s="108"/>
+      <c r="R17" s="108"/>
+      <c r="S17" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="T17" s="19"/>
+      <c r="U17" s="17"/>
+      <c r="V17" s="51"/>
       <c r="W17"/>
-      <c r="X17" s="85"/>
-    </row>
-    <row r="18" spans="1:24" s="89" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A18" s="87"/>
-      <c r="B18" s="88"/>
-      <c r="D18" s="90"/>
-      <c r="E18" s="91"/>
-      <c r="F18" s="92"/>
-      <c r="G18" s="90"/>
-      <c r="I18" s="87"/>
-      <c r="K18" s="91"/>
-      <c r="L18" s="90"/>
-      <c r="M18" s="90"/>
-      <c r="N18" s="90"/>
-      <c r="O18" s="90"/>
-      <c r="P18" s="90"/>
-      <c r="Q18" s="87"/>
-      <c r="S18" s="90"/>
-      <c r="T18" s="90"/>
-      <c r="U18" s="90"/>
-      <c r="V18" s="96"/>
-      <c r="X18" s="90"/>
+      <c r="X17" s="17"/>
+    </row>
+    <row r="18" spans="1:24" s="20" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
+      <c r="A18" s="21"/>
+      <c r="B18" s="33"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="37"/>
+      <c r="I18" s="21"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="37"/>
+      <c r="M18" s="37"/>
+      <c r="N18" s="37"/>
+      <c r="O18" s="37"/>
+      <c r="P18" s="37"/>
+      <c r="Q18" s="21"/>
+      <c r="S18" s="37"/>
+      <c r="T18" s="37"/>
+      <c r="U18" s="37"/>
+      <c r="V18" s="98"/>
+      <c r="X18" s="37"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
-      <c r="B19" s="93"/>
+      <c r="B19" s="31"/>
       <c r="D19" s="1"/>
-      <c r="E19" s="94"/>
-      <c r="F19" s="95"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="14"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="112" t="s">
-        <v>69</v>
-      </c>
-      <c r="K19" s="112"/>
+      <c r="J19" s="103" t="s">
+        <v>53</v>
+      </c>
+      <c r="K19" s="103"/>
       <c r="M19"/>
       <c r="N19" s="1"/>
-      <c r="O19" s="8"/>
+      <c r="O19" s="12"/>
       <c r="T19"/>
       <c r="U19"/>
       <c r="V19" s="97"/>
@@ -2463,67 +2440,67 @@
     </row>
     <row r="20" spans="1:24" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
-      <c r="B20" s="83" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" s="84" t="s">
-        <v>81</v>
-      </c>
-      <c r="D20" s="85"/>
-      <c r="E20" s="83" t="s">
-        <v>71</v>
-      </c>
-      <c r="F20" s="84" t="s">
-        <v>82</v>
-      </c>
-      <c r="G20" s="85"/>
-      <c r="H20" s="85"/>
-      <c r="I20" s="85"/>
-      <c r="J20" s="112"/>
-      <c r="K20" s="112"/>
-      <c r="L20" s="84" t="s">
-        <v>83</v>
-      </c>
-      <c r="M20" s="86"/>
-      <c r="N20" s="85"/>
-      <c r="O20" s="85"/>
-      <c r="P20" s="85"/>
+      <c r="B20" s="35" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="D20" s="17"/>
+      <c r="E20" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="F20" s="41" t="s">
+        <v>85</v>
+      </c>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="103"/>
+      <c r="K20" s="103"/>
+      <c r="L20" s="41" t="s">
+        <v>86</v>
+      </c>
+      <c r="M20" s="19"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
       <c r="T20"/>
       <c r="U20"/>
       <c r="V20" s="97"/>
       <c r="W20"/>
       <c r="X20"/>
     </row>
-    <row r="21" spans="1:24" s="89" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="87"/>
-      <c r="B21" s="88"/>
-      <c r="D21" s="90"/>
-      <c r="E21" s="91"/>
-      <c r="F21" s="92"/>
-      <c r="G21" s="90"/>
-      <c r="I21" s="87"/>
-      <c r="K21" s="91"/>
-      <c r="L21" s="90"/>
-      <c r="M21" s="90"/>
-      <c r="N21" s="90"/>
-      <c r="O21" s="90"/>
-      <c r="P21" s="90"/>
-      <c r="Q21" s="87"/>
-      <c r="V21" s="96"/>
-      <c r="X21" s="90"/>
+    <row r="21" spans="1:24" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="21"/>
+      <c r="B21" s="33"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="37"/>
+      <c r="I21" s="21"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="37"/>
+      <c r="M21" s="37"/>
+      <c r="N21" s="37"/>
+      <c r="O21" s="37"/>
+      <c r="P21" s="37"/>
+      <c r="Q21" s="21"/>
+      <c r="V21" s="98"/>
+      <c r="X21" s="37"/>
     </row>
     <row r="22" spans="1:24" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
-      <c r="B22" s="93"/>
+      <c r="B22" s="31"/>
       <c r="D22" s="1"/>
-      <c r="E22" s="94"/>
-      <c r="F22" s="95"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="14"/>
       <c r="I22" s="1"/>
       <c r="J22"/>
-      <c r="K22" s="12"/>
+      <c r="K22" s="32"/>
       <c r="M22"/>
       <c r="N22" s="1"/>
-      <c r="O22" s="8"/>
+      <c r="O22" s="12"/>
       <c r="T22"/>
       <c r="U22"/>
       <c r="V22" s="97"/>
@@ -2532,107 +2509,141 @@
     </row>
     <row r="23" spans="1:24" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
-      <c r="B23" s="83" t="s">
-        <v>72</v>
-      </c>
-      <c r="C23" s="84" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" s="85"/>
-      <c r="E23" s="83" t="s">
-        <v>73</v>
-      </c>
-      <c r="F23" s="84" t="s">
-        <v>85</v>
-      </c>
-      <c r="G23" s="85"/>
-      <c r="H23" s="85"/>
-      <c r="I23" s="85"/>
-      <c r="J23" s="85"/>
-      <c r="K23" s="85"/>
-      <c r="L23" s="85"/>
-      <c r="M23" s="85"/>
-      <c r="N23" s="85"/>
-      <c r="O23" s="85"/>
+      <c r="B23" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="17"/>
+      <c r="E23" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="17"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
       <c r="T23"/>
       <c r="U23"/>
       <c r="V23" s="97"/>
       <c r="W23"/>
       <c r="X23"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="F24" s="1"/>
+    <row r="24" spans="1:24" s="20" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
+      <c r="B24" s="21"/>
+      <c r="D24" s="37"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="34"/>
+      <c r="J24" s="34"/>
+      <c r="K24" s="34"/>
+      <c r="L24" s="21"/>
+      <c r="M24" s="37"/>
+      <c r="N24" s="37"/>
+      <c r="O24" s="37"/>
+      <c r="P24" s="37"/>
+      <c r="R24" s="21"/>
+      <c r="S24" s="21"/>
+      <c r="V24" s="98"/>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="E25" s="1"/>
       <c r="F25" s="1"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="1"/>
+      <c r="M25"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="1"/>
+      <c r="R25"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="12"/>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="F26" s="1"/>
+      <c r="U26" s="12"/>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="F27" s="1"/>
+      <c r="U27" s="12"/>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="F28" s="1"/>
+      <c r="U28" s="12"/>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="F29" s="1"/>
+      <c r="U29" s="12"/>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="F30" s="1"/>
+      <c r="U30" s="12"/>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
       <c r="F31" s="1"/>
+      <c r="U31" s="12"/>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="F32" s="1"/>
-    </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="U32" s="12"/>
+    </row>
+    <row r="33" spans="6:21" x14ac:dyDescent="0.2">
       <c r="F33" s="1"/>
-    </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="U33" s="12"/>
+    </row>
+    <row r="34" spans="6:21" x14ac:dyDescent="0.2">
       <c r="F34" s="1"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="6:21" x14ac:dyDescent="0.2">
       <c r="F35" s="1"/>
     </row>
-    <row r="36" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="6:21" x14ac:dyDescent="0.2">
       <c r="F36" s="1"/>
     </row>
-    <row r="37" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="6:21" x14ac:dyDescent="0.2">
       <c r="F37" s="1"/>
     </row>
-    <row r="38" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="6:21" x14ac:dyDescent="0.2">
       <c r="F38" s="1"/>
     </row>
-    <row r="39" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="6:21" x14ac:dyDescent="0.2">
       <c r="F39" s="1"/>
     </row>
-    <row r="40" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="6:21" x14ac:dyDescent="0.2">
       <c r="F40" s="1"/>
     </row>
-    <row r="41" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="6:21" x14ac:dyDescent="0.2">
       <c r="F41" s="1"/>
     </row>
-    <row r="42" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="6:21" x14ac:dyDescent="0.2">
       <c r="F42" s="1"/>
     </row>
-    <row r="43" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="6:21" x14ac:dyDescent="0.2">
       <c r="F43" s="1"/>
     </row>
-    <row r="44" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="6:21" x14ac:dyDescent="0.2">
       <c r="F44" s="1"/>
     </row>
-    <row r="45" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="6:21" x14ac:dyDescent="0.2">
       <c r="F45" s="1"/>
     </row>
-    <row r="46" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="6:21" x14ac:dyDescent="0.2">
       <c r="F46" s="1"/>
     </row>
-    <row r="47" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="6:21" x14ac:dyDescent="0.2">
       <c r="F47" s="1"/>
     </row>
-    <row r="48" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="6:21" x14ac:dyDescent="0.2">
       <c r="F48" s="1"/>
     </row>
     <row r="49" spans="6:6" x14ac:dyDescent="0.2">
@@ -2814,42 +2825,99 @@
     </row>
     <row r="108" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F108" s="1"/>
+    </row>
+    <row r="109" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F109" s="1"/>
+    </row>
+    <row r="110" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F110" s="1"/>
+    </row>
+    <row r="111" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F111" s="1"/>
+    </row>
+    <row r="112" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F112" s="1"/>
+    </row>
+    <row r="113" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F113" s="1"/>
+    </row>
+    <row r="114" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F114" s="1"/>
+    </row>
+    <row r="115" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F115" s="1"/>
+    </row>
+    <row r="116" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F116" s="1"/>
+    </row>
+    <row r="117" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F117" s="1"/>
+    </row>
+    <row r="118" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F118" s="1"/>
+    </row>
+    <row r="119" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F119" s="1"/>
+    </row>
+    <row r="120" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F120" s="1"/>
+    </row>
+    <row r="121" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F121" s="1"/>
+    </row>
+    <row r="122" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F122" s="1"/>
+    </row>
+    <row r="123" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F123" s="1"/>
+    </row>
+    <row r="124" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F124" s="1"/>
+    </row>
+    <row r="125" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F125" s="1"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="14">
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="K3:O3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="J16:K17"/>
+    <mergeCell ref="K1:V1"/>
+    <mergeCell ref="J19:K20"/>
+    <mergeCell ref="T6:T7"/>
+    <mergeCell ref="S6:S7"/>
+    <mergeCell ref="Q16:R17"/>
+    <mergeCell ref="K6:M6"/>
+    <mergeCell ref="O6:Q6"/>
     <mergeCell ref="U6:V7"/>
     <mergeCell ref="U10:V10"/>
-    <mergeCell ref="J19:K20"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:M6"/>
-    <mergeCell ref="N6:R6"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
   </mergeCells>
-  <conditionalFormatting sqref="D8">
-    <cfRule type="expression" dxfId="1" priority="8" stopIfTrue="1">
+  <conditionalFormatting sqref="C8:D8">
+    <cfRule type="expression" dxfId="2" priority="7" stopIfTrue="1">
+      <formula>AND((#REF!),#REF!,#REF!)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D10:E10">
+    <cfRule type="expression" dxfId="1" priority="11" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:F13">
-    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="5" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation showErrorMessage="1" sqref="H4 F23 C20 C17 S17 L17 F17 F20 C23 L20" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
-    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="F10 H11:H13" xr:uid="{00000000-0002-0000-0000-000001000000}">
+  <dataValidations count="4">
+    <dataValidation showErrorMessage="1" sqref="F23 K4 C20 C17 S17 L17 F17 F20 C23 L20" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="H10" xr:uid="{00000000-0002-0000-0000-000001000000}"/>
+    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="G16 H11:H13" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I8" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I8" xr:uid="{00000000-0002-0000-0000-000003000000}">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
@@ -2858,8 +2926,8 @@
     <hyperlink ref="A3" r:id="rId1" display="www.federation.org" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="A4" r:id="rId2" display="records@federation.org" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
-  <pageMargins left="0.31496062992125984" right="0.35433070866141736" top="0.39370078740157483" bottom="0.47244094488188981" header="0.51181102362204722" footer="0.23622047244094491"/>
-  <pageSetup scale="57" firstPageNumber="0" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId3"/>
+  <pageMargins left="0.31496062992125984" right="0.35433070866141736" top="0.39370078740157483" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.31496062992125984"/>
+  <pageSetup scale="67" firstPageNumber="0" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId3"/>
   <headerFooter alignWithMargins="0"/>
   <legacyDrawing r:id="rId4"/>
 </worksheet>

--- a/owlcms/src/main/resources/templates/protocol/SnCJTot-LETTER.xlsx
+++ b/owlcms/src/main/resources/templates/protocol/SnCJTot-LETTER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\protocol\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms_v23\owlcms\src\main\resources\templates\protocol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6EC30F3-0197-40D2-8F68-F7920B6AFE0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990FDBEA-2088-44ED-9F11-1A3816ADC08C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2400" yWindow="7425" windowWidth="24615" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="5295" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -146,7 +146,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="95">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -421,10 +421,16 @@
     <t>${session.jury1AsTO} ${session.jury1AsTO.federationId}</t>
   </si>
   <si>
-    <t>${session.jury2AsTO} ${session.jury2AsTO.federationId} ${session.jury3AsTO} ${session.jury3AsTO.federationId} ${session.jury4AsTO} ${session.jury4AsTO.federationId} ${session.jury5AsTO} ${session.jury5AsTO.federationId}</t>
-  </si>
-  <si>
     <t>${session.announcerAsTO} ${session.announcerAsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${t.get("Reserve")}</t>
+  </si>
+  <si>
+    <t>${session.reserveAsTO} ${session.reserveAsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.jury2AsTO} ${session.jury2AsTO.federationId} ${session.jury3AsTO} ${session.jury3AsTO.federationId} ${session.jury4AsTO} ${session.jury4AsTO.federationId} ${session.jury5AsTO} ${session.jury5AsTO.federationId} ${session.reserveJuryAsTO != null ? "("+t.get("Reserve")+") "+session.reserveJuryAsTO+" "+session.reserveJuryAsTO.federationId : ""}</t>
   </si>
 </sst>
 </file>
@@ -1046,7 +1052,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1314,13 +1320,36 @@
     <xf numFmtId="0" fontId="31" fillId="13" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -1338,18 +1367,10 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1368,21 +1389,11 @@
     <xf numFmtId="168" fontId="12" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Accent1" xfId="1" builtinId="29" customBuiltin="1"/>
@@ -1901,20 +1912,20 @@
       <c r="J1" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="102" t="s">
+      <c r="K1" s="109" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
+      <c r="L1" s="109"/>
+      <c r="M1" s="109"/>
+      <c r="N1" s="109"/>
+      <c r="O1" s="109"/>
+      <c r="P1" s="109"/>
+      <c r="Q1" s="109"/>
+      <c r="R1" s="109"/>
+      <c r="S1" s="109"/>
+      <c r="T1" s="109"/>
+      <c r="U1" s="109"/>
+      <c r="V1" s="109"/>
     </row>
     <row r="2" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="53" t="s">
@@ -1951,13 +1962,13 @@
       <c r="J3" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="120" t="s">
+      <c r="K3" s="106" t="s">
         <v>57</v>
       </c>
-      <c r="L3" s="120"/>
-      <c r="M3" s="120"/>
-      <c r="N3" s="120"/>
-      <c r="O3" s="120"/>
+      <c r="L3" s="106"/>
+      <c r="M3" s="106"/>
+      <c r="N3" s="106"/>
+      <c r="O3" s="106"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="61"/>
       <c r="R3" s="32" t="s">
@@ -1999,32 +2010,32 @@
       <c r="H6" s="7"/>
       <c r="I6" s="9"/>
       <c r="J6" s="7"/>
-      <c r="K6" s="109" t="s">
+      <c r="K6" s="102" t="s">
         <v>38</v>
       </c>
-      <c r="L6" s="110"/>
-      <c r="M6" s="111"/>
+      <c r="L6" s="115"/>
+      <c r="M6" s="103"/>
       <c r="N6" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="O6" s="109" t="s">
+      <c r="O6" s="102" t="s">
         <v>39</v>
       </c>
-      <c r="P6" s="110"/>
-      <c r="Q6" s="111"/>
+      <c r="P6" s="115"/>
+      <c r="Q6" s="103"/>
       <c r="R6" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="S6" s="106" t="s">
+      <c r="S6" s="112" t="s">
         <v>45</v>
       </c>
-      <c r="T6" s="104" t="s">
+      <c r="T6" s="110" t="s">
         <v>46</v>
       </c>
-      <c r="U6" s="112" t="s">
+      <c r="U6" s="116" t="s">
         <v>82</v>
       </c>
-      <c r="V6" s="113"/>
+      <c r="V6" s="117"/>
       <c r="X6"/>
     </row>
     <row r="7" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2040,10 +2051,10 @@
       <c r="D7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="109" t="s">
+      <c r="E7" s="102" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="111"/>
+      <c r="F7" s="103"/>
       <c r="G7" s="11" t="s">
         <v>34</v>
       </c>
@@ -2080,10 +2091,10 @@
       <c r="R7" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="S7" s="107"/>
-      <c r="T7" s="105"/>
-      <c r="U7" s="114"/>
-      <c r="V7" s="115"/>
+      <c r="S7" s="113"/>
+      <c r="T7" s="111"/>
+      <c r="U7" s="118"/>
+      <c r="V7" s="119"/>
     </row>
     <row r="8" spans="1:24" s="28" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="68"/>
@@ -2138,10 +2149,10 @@
       <c r="D10" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="118" t="s">
+      <c r="E10" s="104" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="119"/>
+      <c r="F10" s="105"/>
       <c r="G10" s="66" t="s">
         <v>5</v>
       </c>
@@ -2184,10 +2195,10 @@
       <c r="T10" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="U10" s="116" t="s">
+      <c r="U10" s="120" t="s">
         <v>83</v>
       </c>
-      <c r="V10" s="117"/>
+      <c r="V10" s="121"/>
     </row>
     <row r="11" spans="1:24" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11"/>
@@ -2335,23 +2346,23 @@
       <c r="A16" s="14"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
-      <c r="E16" s="121" t="s">
+      <c r="E16" s="107" t="s">
         <v>48</v>
       </c>
       <c r="G16" s="24"/>
       <c r="H16" s="15"/>
       <c r="I16" s="14"/>
-      <c r="J16" s="103" t="s">
+      <c r="J16" s="108" t="s">
         <v>49</v>
       </c>
-      <c r="K16" s="103"/>
+      <c r="K16" s="108"/>
       <c r="L16" s="14"/>
       <c r="N16" s="16"/>
       <c r="P16" s="14"/>
-      <c r="Q16" s="108" t="s">
+      <c r="Q16" s="114" t="s">
         <v>50</v>
       </c>
-      <c r="R16" s="108"/>
+      <c r="R16" s="114"/>
       <c r="S16" s="47"/>
       <c r="T16" s="14"/>
       <c r="U16" s="12"/>
@@ -2367,18 +2378,18 @@
         <v>47</v>
       </c>
       <c r="C17" s="41" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D17" s="17"/>
-      <c r="E17" s="121"/>
+      <c r="E17" s="107"/>
       <c r="F17" s="41" t="s">
         <v>87</v>
       </c>
       <c r="G17" s="17"/>
       <c r="H17" s="17"/>
       <c r="I17" s="17"/>
-      <c r="J17" s="103"/>
-      <c r="K17" s="103"/>
+      <c r="J17" s="108"/>
+      <c r="K17" s="108"/>
       <c r="L17" s="41" t="s">
         <v>88</v>
       </c>
@@ -2386,8 +2397,8 @@
       <c r="N17" s="17"/>
       <c r="O17" s="17"/>
       <c r="P17" s="19"/>
-      <c r="Q17" s="108"/>
-      <c r="R17" s="108"/>
+      <c r="Q17" s="114"/>
+      <c r="R17" s="114"/>
       <c r="S17" s="41" t="s">
         <v>89</v>
       </c>
@@ -2395,7 +2406,6 @@
       <c r="U17" s="17"/>
       <c r="V17" s="51"/>
       <c r="W17"/>
-      <c r="X17" s="17"/>
     </row>
     <row r="18" spans="1:24" s="20" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
       <c r="A18" s="21"/>
@@ -2416,7 +2426,6 @@
       <c r="T18" s="37"/>
       <c r="U18" s="37"/>
       <c r="V18" s="98"/>
-      <c r="X18" s="37"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
@@ -2425,17 +2434,20 @@
       <c r="E19" s="30"/>
       <c r="F19" s="14"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="103" t="s">
+      <c r="J19" s="108" t="s">
         <v>53</v>
       </c>
-      <c r="K19" s="103"/>
+      <c r="K19" s="108"/>
       <c r="M19"/>
       <c r="N19" s="1"/>
       <c r="O19" s="12"/>
+      <c r="Q19" s="108" t="s">
+        <v>92</v>
+      </c>
+      <c r="R19" s="108"/>
+      <c r="S19" s="1"/>
       <c r="T19"/>
-      <c r="U19"/>
-      <c r="V19" s="97"/>
-      <c r="W19"/>
+      <c r="V19" s="12"/>
       <c r="X19"/>
     </row>
     <row r="20" spans="1:24" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
@@ -2456,8 +2468,8 @@
       <c r="G20" s="17"/>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
-      <c r="J20" s="103"/>
-      <c r="K20" s="103"/>
+      <c r="J20" s="108"/>
+      <c r="K20" s="108"/>
       <c r="L20" s="41" t="s">
         <v>86</v>
       </c>
@@ -2465,10 +2477,14 @@
       <c r="N20" s="17"/>
       <c r="O20" s="17"/>
       <c r="P20" s="17"/>
-      <c r="T20"/>
-      <c r="U20"/>
-      <c r="V20" s="97"/>
-      <c r="W20"/>
+      <c r="Q20" s="108"/>
+      <c r="R20" s="108"/>
+      <c r="S20" s="41" t="s">
+        <v>93</v>
+      </c>
+      <c r="T20" s="19"/>
+      <c r="U20" s="17"/>
+      <c r="V20" s="17"/>
       <c r="X20"/>
     </row>
     <row r="21" spans="1:24" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2487,7 +2503,6 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="21"/>
       <c r="V21" s="98"/>
-      <c r="X21" s="37"/>
     </row>
     <row r="22" spans="1:24" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
@@ -2520,7 +2535,7 @@
         <v>54</v>
       </c>
       <c r="F23" s="41" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G23" s="17"/>
       <c r="H23" s="17"/>
@@ -2530,10 +2545,14 @@
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" s="17"/>
-      <c r="O23" s="17"/>
-      <c r="T23"/>
-      <c r="U23"/>
-      <c r="V23" s="97"/>
+      <c r="O23" s="122"/>
+      <c r="P23" s="122"/>
+      <c r="Q23" s="122"/>
+      <c r="R23" s="122"/>
+      <c r="S23" s="123"/>
+      <c r="T23" s="123"/>
+      <c r="U23" s="123"/>
+      <c r="V23" s="124"/>
       <c r="W23"/>
       <c r="X23"/>
     </row>
@@ -2879,12 +2898,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <mergeCells count="14">
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="K3:O3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="J16:K17"/>
+  <mergeCells count="15">
     <mergeCell ref="K1:V1"/>
     <mergeCell ref="J19:K20"/>
     <mergeCell ref="T6:T7"/>
@@ -2894,6 +2908,12 @@
     <mergeCell ref="O6:Q6"/>
     <mergeCell ref="U6:V7"/>
     <mergeCell ref="U10:V10"/>
+    <mergeCell ref="Q19:R20"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="K3:O3"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="J16:K17"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:D8">
     <cfRule type="expression" dxfId="2" priority="7" stopIfTrue="1">
@@ -2911,7 +2931,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation showErrorMessage="1" sqref="F23 K4 C20 C17 S17 L17 F17 F20 C23 L20" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation showErrorMessage="1" sqref="K4 F23 C20 C17 S17 L17 F17 F20 C23 L20 S20" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
     <dataValidation allowBlank="1" showErrorMessage="1" sqref="H10" xr:uid="{00000000-0002-0000-0000-000001000000}"/>
     <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="G16 H11:H13" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>0</formula1>

--- a/owlcms/src/main/resources/templates/protocol/SnCJTot-LETTER.xlsx
+++ b/owlcms/src/main/resources/templates/protocol/SnCJTot-LETTER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms_v23\owlcms\src\main\resources\templates\protocol\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms4\owlcms\src\main\resources\templates\protocol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990FDBEA-2088-44ED-9F11-1A3816ADC08C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{779383C6-C623-4FF1-9EDA-646DE922C775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5295" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="11505" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -25,21 +25,21 @@
     <definedName name="CategoryFilter">Results!#REF!</definedName>
     <definedName name="CLUB">Results!#REF!</definedName>
     <definedName name="Collet">#REF!</definedName>
-    <definedName name="_xlnm.Criteria" localSheetId="0">Results!$A$1:$CF$99</definedName>
+    <definedName name="_xlnm.Criteria" localSheetId="0">Results!$A$1:$CF$75</definedName>
     <definedName name="demandé">Results!#REF!</definedName>
     <definedName name="dernier">Results!#REF!</definedName>
     <definedName name="essais">Results!#REF!</definedName>
     <definedName name="essaisArr">Results!#REF!</definedName>
     <definedName name="Excel_BuiltIn_Criteria_1">Results!#REF!</definedName>
-    <definedName name="GroupeCourant">Results!$K$4</definedName>
+    <definedName name="GroupeCourant">Results!$H$4</definedName>
     <definedName name="Groupes">#REF!</definedName>
     <definedName name="GroupFilter">Results!#REF!</definedName>
     <definedName name="InactiveGroupFilter">Results!#REF!</definedName>
     <definedName name="isSnatch">Results!#REF!</definedName>
     <definedName name="lbParKg">Results!#REF!</definedName>
-    <definedName name="LignesCalculs">Results!$25:$25</definedName>
+    <definedName name="LignesCalculs">Results!#REF!</definedName>
     <definedName name="LignesEntête">Results!$1:$5</definedName>
-    <definedName name="LignesOfficiels">Results!$17:$24</definedName>
+    <definedName name="LignesOfficiels">Results!$12:$15</definedName>
     <definedName name="M_F">Results!#REF!</definedName>
     <definedName name="NAIS.">Results!#REF!</definedName>
     <definedName name="NbCollet">#REF!</definedName>
@@ -55,14 +55,12 @@
     <definedName name="TAS">Results!#REF!</definedName>
     <definedName name="tirage">Results!#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="181029" iterate="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -76,68 +74,80 @@
     <author>Jean-François Lamy</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{5464D8D0-CD5E-425C-A581-A77008842DB5}">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{CBD6DE4D-1C2E-4747-83CB-FDC2A1E37FF6}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t>jx:area(lastCell="V23")</t>
         </r>
       </text>
     </comment>
-    <comment ref="A8" authorId="0" shapeId="0" xr:uid="{CEBD2170-0D1A-40A3-B9D6-62E3599ECF09}">
+    <comment ref="A8" authorId="0" shapeId="0" xr:uid="{78C9474A-E803-416B-8110-C82A4ADE45B0}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t>jx:each(items="athletes" var="group" groupBy="group.categorySortCode" groupOrder="ASC" lastCell="V10")</t>
         </r>
       </text>
     </comment>
-    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{F0A7DC28-4FBA-4A0F-B1F3-C337DC82D113}">
+    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{8CC34236-0149-42F9-B1CC-CCB1421EA3C0}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="1"/>
           </rPr>
-          <t>jx:each(items="group.items" var="l"  varIndex="lifterLoop" lastCell="V10")</t>
+          <t xml:space="preserve">jx:each(items="group.items" var="l"  varIndex="lifterLoop" lastCell="V10")
+</t>
         </r>
       </text>
     </comment>
-    <comment ref="A12" authorId="0" shapeId="0" xr:uid="{970BB391-BC34-4352-A877-A2663ADBC3A4}">
+    <comment ref="A12" authorId="0" shapeId="0" xr:uid="{4F1B1DD0-0511-44CE-9AD5-6D11674303E8}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="1"/>
           </rPr>
           <t>jx:if(condition="records != null" lastCell="V15")</t>
         </r>
       </text>
     </comment>
-    <comment ref="A15" authorId="0" shapeId="0" xr:uid="{1E324CE8-95D7-4732-87D4-D0D1EB5131F4}">
+    <comment ref="A15" authorId="0" shapeId="0" xr:uid="{2E0ABA1D-29D1-409E-8171-6D58FBB63FC3}">
       <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Jean-François Lamy:</t>
+        </r>
         <r>
           <rPr>
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <family val="2"/>
+            <charset val="1"/>
           </rPr>
-          <t>jx:each(items="records" var="r" lastCell="V15")</t>
+          <t xml:space="preserve">
+jx:each(items="records" var="r" lastCell="V15")</t>
         </r>
       </text>
     </comment>
@@ -146,10 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="95">
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="91">
   <si>
     <t>${l.lotNumber}</t>
   </si>
@@ -223,9 +230,6 @@
     <t>${competition.federationEMail}</t>
   </si>
   <si>
-    <t>${l.startNumber}</t>
-  </si>
-  <si>
     <t>${l.formattedBirth}</t>
   </si>
   <si>
@@ -271,34 +275,97 @@
     <t>${t.get("Results.Membership")}</t>
   </si>
   <si>
-    <t>${t.get("Results.Start")}</t>
-  </si>
-  <si>
-    <t>${t.get("Results.Lot")}</t>
-  </si>
-  <si>
-    <t>${t.get("Results.Best")}</t>
-  </si>
-  <si>
-    <t>${t.get("Results.Snatch_abbrev")}</t>
-  </si>
-  <si>
     <t>${t.get("Results.Total")}</t>
   </si>
   <si>
     <t>${t.get("Results.Rank")}</t>
   </si>
   <si>
+    <t>${competition.localizedCompetitionDate}</t>
+  </si>
+  <si>
+    <t>${t.get("Lot")}</t>
+  </si>
+  <si>
+    <t>${t.get("Results.max")}</t>
+  </si>
+  <si>
+    <t>${l.snatchRank}</t>
+  </si>
+  <si>
+    <t>${l.cleanJerkRank}</t>
+  </si>
+  <si>
+    <t>${l.totalRank}</t>
+  </si>
+  <si>
+    <t>${group.item.displayCategory}</t>
+  </si>
+  <si>
+    <t>${t.get("Preparation.Records")}</t>
+  </si>
+  <si>
+    <t>${t.get("Results.RecordFederation")}</t>
+  </si>
+  <si>
+    <t>${t.get("Results.RecordName")}</t>
+  </si>
+  <si>
+    <t>${t.get("Results.RecordAgeGroup")}</t>
+  </si>
+  <si>
+    <t>${t.get("Results.RecordKind")}</t>
+  </si>
+  <si>
+    <t>${t.get("Results.RecordWeight")}</t>
+  </si>
+  <si>
+    <t>${t.get("Name")}</t>
+  </si>
+  <si>
+    <t>${t.get("Group")}</t>
+  </si>
+  <si>
+    <t>${t.get("Results.RecordDate")}</t>
+  </si>
+  <si>
+    <t>${r.recordFederation}</t>
+  </si>
+  <si>
+    <t>${r.recordName}</t>
+  </si>
+  <si>
+    <t>${r.recordValue}</t>
+  </si>
+  <si>
+    <t>${r.nation}</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ${r.birth}</t>
+  </si>
+  <si>
+    <t>${r.groupNameString}</t>
+  </si>
+  <si>
+    <t>${r.recordDateAsString}</t>
+  </si>
+  <si>
+    <t>${r.ageGrp} ${r.gender}</t>
+  </si>
+  <si>
+    <t>${r.bwCatString}</t>
+  </si>
+  <si>
+    <t>${r.resAthleteName}</t>
+  </si>
+  <si>
+    <t>${r.resRecordLift}</t>
+  </si>
+  <si>
     <t>${t.get("Announcer")}</t>
   </si>
   <si>
-    <t>${t.get("Marshall")}</t>
-  </si>
-  <si>
-    <t>${t.get("Timekeeper")}</t>
-  </si>
-  <si>
-    <t>${t.get("Results.Controller")}</t>
+    <t>${t.get("Referee3")}</t>
   </si>
   <si>
     <t>${t.get("Referee1")}</t>
@@ -307,87 +374,12 @@
     <t>${t.get("Referee2")}</t>
   </si>
   <si>
-    <t>${t.get("Referee3")}</t>
+    <t>${t.get("JuryPresident")}</t>
   </si>
   <si>
     <t>${t.get("Jury")}</t>
   </si>
   <si>
-    <t>${t.get("Results.CJ_abbrev")}</t>
-  </si>
-  <si>
-    <t>${group.item.category}</t>
-  </si>
-  <si>
-    <t>${competition.localizedCompetitionDate}</t>
-  </si>
-  <si>
-    <t>${r.recordFederation}</t>
-  </si>
-  <si>
-    <t>${r.recordName}</t>
-  </si>
-  <si>
-    <t>${r.recordValue}</t>
-  </si>
-  <si>
-    <t>${r.nation}</t>
-  </si>
-  <si>
-    <t>${r.recordDateAsString}</t>
-  </si>
-  <si>
-    <t>${r.groupNameString}</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ${r.birth}</t>
-  </si>
-  <si>
-    <t>${t.get("Preparation.Records")}</t>
-  </si>
-  <si>
-    <t>${t.get("Group")}</t>
-  </si>
-  <si>
-    <t>${t.get("Name")}</t>
-  </si>
-  <si>
-    <t>${t.get("Results.RecordName")}</t>
-  </si>
-  <si>
-    <t>${t.get("Results.RecordWeight")}</t>
-  </si>
-  <si>
-    <t>${t.get("Results.RecordDate")}</t>
-  </si>
-  <si>
-    <t>${t.get("JuryPresident")}</t>
-  </si>
-  <si>
-    <t>${t.get("Results.RecordAgeGroup")}</t>
-  </si>
-  <si>
-    <t>${t.get("Results.RecordFederation")}</t>
-  </si>
-  <si>
-    <t>${t.get("Results.RecordKind")}</t>
-  </si>
-  <si>
-    <t>${r.bwCatString}</t>
-  </si>
-  <si>
-    <t>${r.ageGrp} ${r.gender}</t>
-  </si>
-  <si>
-    <t>${r.resAthleteName}</t>
-  </si>
-  <si>
-    <t>${r.resRecordLift}</t>
-  </si>
-  <si>
-    <t>${l.totalRank &lt; 0 ? "inv." : (l.totalRank &gt; 0 ? l.totalRank : "" )}</t>
-  </si>
-  <si>
     <t>${session != null ? t.get("Group") + " :" : ""}</t>
   </si>
   <si>
@@ -400,6 +392,15 @@
     <t>${l.bestLifterScore}</t>
   </si>
   <si>
+    <t>${session.marshallAsTO} ${session.marshallAsTO.federationId} ${session.marshal2AsTO} ${session.marshal2AsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.timeKeeperAsTO} ${session.timeKeeperAsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.technicalControllerAsTO} ${session.technicalControllerAsTO.federationId} ${session.technicalController2AsTO} ${session.technicalController2AsTO.federationId}</t>
+  </si>
+  <si>
     <t>${session.referee1AsTO} ${session.referee1AsTO.federationId}</t>
   </si>
   <si>
@@ -409,15 +410,6 @@
     <t>${session.referee3AsTO} ${session.referee3AsTO.federationId}</t>
   </si>
   <si>
-    <t>${session.marshallAsTO} ${session.marshallAsTO.federationId} ${session.marshal2AsTO} ${session.marshal2AsTO.federationId}</t>
-  </si>
-  <si>
-    <t>${session.timeKeeperAsTO} ${session.timeKeeperAsTO.federationId}</t>
-  </si>
-  <si>
-    <t>${session.technicalControllerAsTO} ${session.technicalControllerAsTO.federationId} ${session.technicalController2AsTO} ${session.technicalController2AsTO.federationId}</t>
-  </si>
-  <si>
     <t>${session.jury1AsTO} ${session.jury1AsTO.federationId}</t>
   </si>
   <si>
@@ -430,22 +422,25 @@
     <t>${session.reserveAsTO} ${session.reserveAsTO.federationId}</t>
   </si>
   <si>
-    <t>${session.jury2AsTO} ${session.jury2AsTO.federationId} ${session.jury3AsTO} ${session.jury3AsTO.federationId} ${session.jury4AsTO} ${session.jury4AsTO.federationId} ${session.jury5AsTO} ${session.jury5AsTO.federationId} ${session.reserveJuryAsTO != null ? "("+t.get("Reserve")+") "+session.reserveJuryAsTO+" "+session.reserveJuryAsTO.federationId : ""}</t>
+    <t>${t.get("ReserveJury")}</t>
+  </si>
+  <si>
+    <t>${session.jury2AsTO} ${session.jury2AsTO.federationId} ${session.jury3AsTO} ${session.jury3AsTO.federationId} ${session.jury4AsTO} ${session.jury4AsTO.federationId} ${session.jury5AsTO} ${session.jury5AsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${session.reserveJuryAsTO} ${session.reserveJuryAsTO.federationId}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
-    <numFmt numFmtId="164" formatCode="0.0;;"/>
-    <numFmt numFmtId="165" formatCode="_ * #,##0_)\ _$_ ;_ * \(#,##0&quot;) &quot;_$_ ;_ * \-??_)\ _$_ ;_ @_ "/>
-    <numFmt numFmtId="166" formatCode="_-#,##0;[Red]\(#,##0\);\-"/>
-    <numFmt numFmtId="167" formatCode="0;\(0\);\-"/>
-    <numFmt numFmtId="168" formatCode="0.000;;\-"/>
-    <numFmt numFmtId="169" formatCode="0;\-;\-"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="_-#,##0;[Red]\(#,##0\);\-"/>
+    <numFmt numFmtId="165" formatCode="0;\(0\);\-"/>
+    <numFmt numFmtId="166" formatCode="0.000;;\-"/>
   </numFmts>
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="35" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -527,18 +522,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="7"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -586,6 +569,18 @@
     <font>
       <sz val="10"/>
       <color indexed="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -610,6 +605,12 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -633,16 +634,29 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -710,6 +724,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+        <bgColor indexed="26"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="31"/>
       </patternFill>
@@ -721,7 +741,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -767,6 +787,26 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color indexed="8"/>
       </top>
@@ -775,11 +815,9 @@
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
+      <right/>
       <top style="thin">
-        <color indexed="8"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
         <color indexed="64"/>
@@ -788,21 +826,19 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="8"/>
+        <color indexed="64"/>
       </left>
       <right/>
       <top style="thin">
-        <color indexed="8"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="8"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -817,23 +853,12 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color indexed="8"/>
-      </right>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -845,7 +870,7 @@
       </right>
       <top/>
       <bottom style="thin">
-        <color indexed="8"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -854,8 +879,21 @@
       <right style="thin">
         <color indexed="8"/>
       </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
       <top style="thin">
-        <color indexed="8"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
         <color indexed="8"/>
@@ -863,8 +901,12 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="8"/>
       </top>
@@ -874,8 +916,12 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -886,69 +932,86 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color indexed="8"/>
+      </left>
+      <right style="thin">
+        <color indexed="8"/>
+      </right>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
       </left>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
+        <color indexed="8"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color indexed="8"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color indexed="64"/>
+        <color indexed="8"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color indexed="8"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color indexed="8"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color indexed="8"/>
       </right>
       <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color indexed="8"/>
       </right>
       <top/>
       <bottom style="thin">
@@ -961,7 +1024,7 @@
         <color indexed="8"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color indexed="8"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
@@ -973,9 +1036,18 @@
       <left style="thin">
         <color indexed="8"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
+      <right/>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -1044,7 +1116,7 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1052,7 +1124,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1070,129 +1142,25 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right"/>
-      <protection locked="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1201,8 +1169,11 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1">
@@ -1214,7 +1185,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1223,177 +1194,260 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="12" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="9" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="20" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="12" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="23" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="12" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="12" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="12" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="8" xfId="12" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="9" xfId="12" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="12" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="12" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="14" xfId="12" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="12" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="15" xfId="12" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Accent1" xfId="1" builtinId="29" customBuiltin="1"/>
@@ -1416,15 +1470,7 @@
     <cellStyle name="Titre de la feuille" xfId="17" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1873,17 +1919,17 @@
   <sheetPr codeName="Feuil4">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X125"/>
+  <dimension ref="A1:X101"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="1"/>
     <col min="2" max="2" width="5.42578125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" customWidth="1"/>
-    <col min="5" max="5" width="20.28515625" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" customWidth="1"/>
     <col min="6" max="6" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12" style="1" customWidth="1"/>
     <col min="9" max="9" width="10.28515625" style="2" customWidth="1"/>
     <col min="10" max="10" width="10.42578125" style="1" customWidth="1"/>
     <col min="11" max="13" width="7.7109375" style="1" customWidth="1"/>
@@ -1892,313 +1938,323 @@
     <col min="16" max="18" width="7.7109375" style="1" customWidth="1"/>
     <col min="19" max="19" width="7.7109375" customWidth="1"/>
     <col min="20" max="20" width="8.42578125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="7" style="1" customWidth="1"/>
-    <col min="22" max="22" width="7" style="3" customWidth="1"/>
+    <col min="21" max="22" width="7" style="1" customWidth="1"/>
     <col min="23" max="23" width="10.140625" style="1" customWidth="1"/>
     <col min="24" max="24" width="8.140625" style="1" hidden="1" customWidth="1"/>
     <col min="25" max="25" width="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="116" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="116"/>
+      <c r="J1" s="116"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="116"/>
+      <c r="N1" s="116"/>
+      <c r="O1" s="116"/>
+      <c r="P1" s="116"/>
+      <c r="Q1" s="116"/>
+      <c r="R1" s="116"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
+      <c r="V1" s="116"/>
+    </row>
+    <row r="2" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="15"/>
-      <c r="J1" s="32" t="s">
+      <c r="B2" s="19"/>
+      <c r="C2" s="4"/>
+      <c r="G2" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="113"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" s="114" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q2" s="115"/>
+      <c r="R2" s="115"/>
+      <c r="S2" s="1"/>
+    </row>
+    <row r="3" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="25"/>
+      <c r="G3" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="109" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" s="109"/>
-      <c r="M1" s="109"/>
-      <c r="N1" s="109"/>
-      <c r="O1" s="109"/>
-      <c r="P1" s="109"/>
-      <c r="Q1" s="109"/>
-      <c r="R1" s="109"/>
-      <c r="S1" s="109"/>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
-      <c r="V1" s="109"/>
-    </row>
-    <row r="2" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="53" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="4"/>
-      <c r="J2" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="55" t="s">
+      <c r="H3" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q3" s="28"/>
+      <c r="R3" s="28"/>
+      <c r="S3" s="29"/>
+      <c r="T3" s="29"/>
+      <c r="U3" s="29"/>
+      <c r="V3" s="29"/>
+    </row>
+    <row r="4" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="99"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="52"/>
-      <c r="O2" s="52"/>
-      <c r="P2" s="57"/>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="S2" t="s">
-        <v>18</v>
-      </c>
-      <c r="T2" s="58"/>
-      <c r="U2" s="58"/>
-    </row>
-    <row r="3" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="59" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="60"/>
-      <c r="J3" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" s="106" t="s">
-        <v>57</v>
-      </c>
-      <c r="L3" s="106"/>
-      <c r="M3" s="106"/>
-      <c r="N3" s="106"/>
-      <c r="O3" s="106"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="61"/>
-      <c r="R3" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="S3" s="62" t="s">
-        <v>19</v>
-      </c>
-      <c r="T3" s="63"/>
-      <c r="U3" s="63"/>
-      <c r="V3" s="96"/>
-    </row>
-    <row r="4" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="59" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" s="59"/>
-      <c r="C4" s="48"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="12"/>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
-      <c r="J4" s="32" t="s">
-        <v>80</v>
-      </c>
-      <c r="K4" s="100" t="s">
-        <v>81</v>
-      </c>
-      <c r="L4"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="Q4"/>
-      <c r="R4" s="32"/>
-      <c r="S4" s="64"/>
+      <c r="G4" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4"/>
+      <c r="J4" s="3"/>
+      <c r="O4" s="11"/>
+      <c r="P4" s="30"/>
+      <c r="S4" s="1"/>
     </row>
     <row r="5" spans="1:24" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="6" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="7"/>
-      <c r="C6" s="8"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="102" t="s">
+      <c r="A6" s="105" t="s">
         <v>38</v>
       </c>
-      <c r="L6" s="115"/>
-      <c r="M6" s="103"/>
-      <c r="N6" s="42" t="s">
+      <c r="B6" s="105" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="107" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="109" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="101" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="101" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="101" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="101" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="103" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" s="104"/>
+      <c r="K6" s="104"/>
+      <c r="L6" s="104"/>
+      <c r="M6" s="104"/>
+      <c r="N6" s="103" t="s">
+        <v>37</v>
+      </c>
+      <c r="O6" s="104"/>
+      <c r="P6" s="104"/>
+      <c r="Q6" s="104"/>
+      <c r="R6" s="104"/>
+      <c r="S6" s="99" t="s">
+        <v>39</v>
+      </c>
+      <c r="T6" s="100"/>
+      <c r="U6" s="92" t="s">
+        <v>76</v>
+      </c>
+      <c r="V6" s="93"/>
+      <c r="X6"/>
+    </row>
+    <row r="7" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="106"/>
+      <c r="B7" s="106"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="110"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="102"/>
+      <c r="H7" s="102"/>
+      <c r="I7" s="41">
+        <v>1</v>
+      </c>
+      <c r="J7" s="40">
+        <v>2</v>
+      </c>
+      <c r="K7" s="40">
+        <v>3</v>
+      </c>
+      <c r="L7" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="O6" s="102" t="s">
+      <c r="M7" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="N7" s="40">
+        <v>1</v>
+      </c>
+      <c r="O7" s="40">
+        <v>2</v>
+      </c>
+      <c r="P7" s="40">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="R7" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="S7" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="P6" s="115"/>
-      <c r="Q6" s="103"/>
-      <c r="R6" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="S6" s="112" t="s">
+      <c r="T7" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="U7" s="94"/>
+      <c r="V7" s="95"/>
+    </row>
+    <row r="8" spans="1:24" s="10" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="32"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="34"/>
+    </row>
+    <row r="9" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9" s="54"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="37"/>
+      <c r="N9" s="37"/>
+      <c r="O9" s="37"/>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="37"/>
+      <c r="R9" s="37"/>
+      <c r="S9" s="37"/>
+      <c r="T9" s="37"/>
+      <c r="U9" s="37"/>
+      <c r="V9" s="38"/>
+      <c r="X9"/>
+    </row>
+    <row r="10" spans="1:24" s="10" customFormat="1" ht="21.2" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="46" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="K10" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="L10" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="M10" s="51" t="s">
+        <v>44</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="P10" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q10" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="T6" s="110" t="s">
+      <c r="S10" s="52" t="s">
+        <v>6</v>
+      </c>
+      <c r="T10" s="53" t="s">
         <v>46</v>
       </c>
-      <c r="U6" s="116" t="s">
-        <v>82</v>
-      </c>
-      <c r="V6" s="117"/>
-      <c r="X6"/>
-    </row>
-    <row r="7" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="102" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="103"/>
-      <c r="G7" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="I7" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="K7" s="10">
-        <v>1</v>
-      </c>
-      <c r="L7" s="10">
-        <v>2</v>
-      </c>
-      <c r="M7" s="10">
-        <v>3</v>
-      </c>
-      <c r="N7" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="O7" s="10">
-        <v>1</v>
-      </c>
-      <c r="P7" s="10">
-        <v>2</v>
-      </c>
-      <c r="Q7" s="10">
-        <v>3</v>
-      </c>
-      <c r="R7" s="45" t="s">
-        <v>55</v>
-      </c>
-      <c r="S7" s="113"/>
-      <c r="T7" s="111"/>
-      <c r="U7" s="118"/>
-      <c r="V7" s="119"/>
-    </row>
-    <row r="8" spans="1:24" s="28" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="68"/>
-      <c r="B8" s="68"/>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="69"/>
-      <c r="K8" s="70"/>
-    </row>
-    <row r="9" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="71" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" s="72"/>
-      <c r="C9" s="73"/>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="73"/>
-      <c r="H9" s="73"/>
-      <c r="I9" s="73"/>
-      <c r="J9" s="73"/>
-      <c r="K9" s="73"/>
-      <c r="L9" s="73"/>
-      <c r="M9" s="73"/>
-      <c r="N9" s="73"/>
-      <c r="O9" s="73"/>
-      <c r="P9" s="73"/>
-      <c r="Q9" s="73"/>
-      <c r="R9" s="73"/>
-      <c r="S9" s="73"/>
-      <c r="T9" s="73"/>
-      <c r="U9" s="73"/>
-      <c r="V9" s="101"/>
-      <c r="X9"/>
-    </row>
-    <row r="10" spans="1:24" s="28" customFormat="1" ht="21.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="104" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="105"/>
-      <c r="G10" s="66" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" s="67" t="s">
-        <v>6</v>
-      </c>
-      <c r="J10" s="65" t="s">
-        <v>26</v>
-      </c>
-      <c r="K10" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="L10" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="M10" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="N10" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="O10" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="P10" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q10" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="R10" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="S10" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="T10" s="46" t="s">
-        <v>79</v>
-      </c>
-      <c r="U10" s="120" t="s">
-        <v>83</v>
-      </c>
-      <c r="V10" s="121"/>
+      <c r="U10" s="96" t="s">
+        <v>77</v>
+      </c>
+      <c r="V10" s="97"/>
     </row>
     <row r="11" spans="1:24" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11"/>
@@ -2218,324 +2274,290 @@
       <c r="W11"/>
       <c r="X11"/>
     </row>
-    <row r="12" spans="1:24" s="49" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A12" s="49" t="s">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="J12" s="14"/>
+    </row>
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="55"/>
+      <c r="B13" s="55"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="55"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="55"/>
+      <c r="L13" s="55"/>
+      <c r="M13" s="55"/>
+      <c r="N13" s="55"/>
+      <c r="O13" s="55"/>
+      <c r="P13" s="56"/>
+      <c r="Q13" s="56"/>
+      <c r="R13" s="56"/>
+      <c r="S13" s="55"/>
+      <c r="T13" s="55"/>
+      <c r="U13" s="56"/>
+      <c r="V13" s="56"/>
+    </row>
+    <row r="14" spans="1:24" s="66" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A14" s="57" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="58"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="61" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="60" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="62" t="s">
+        <v>52</v>
+      </c>
+      <c r="H14" s="63"/>
+      <c r="I14" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="J14" s="57" t="s">
+        <v>54</v>
+      </c>
+      <c r="K14" s="64"/>
+      <c r="L14" s="58"/>
+      <c r="M14" s="59"/>
+      <c r="N14" s="57" t="s">
+        <v>34</v>
+      </c>
+      <c r="O14" s="58"/>
+      <c r="P14" s="65"/>
+      <c r="Q14" s="57" t="s">
+        <v>35</v>
+      </c>
+      <c r="R14" s="58"/>
+      <c r="S14" s="57" t="s">
+        <v>55</v>
+      </c>
+      <c r="T14" s="64"/>
+      <c r="U14" s="57" t="s">
+        <v>56</v>
+      </c>
+      <c r="V14" s="65"/>
+      <c r="X14" s="59"/>
+    </row>
+    <row r="15" spans="1:24" s="74" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="67" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="68"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="70" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="71" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" s="76" t="s">
         <v>65</v>
       </c>
-      <c r="J12" s="50"/>
-    </row>
-    <row r="13" spans="1:24" s="49" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="75"/>
-      <c r="B13" s="75"/>
-      <c r="C13" s="75"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="75"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75"/>
-      <c r="J13" s="81"/>
-      <c r="K13" s="75"/>
-      <c r="L13" s="75"/>
-      <c r="M13" s="75"/>
-      <c r="N13" s="75"/>
-      <c r="O13" s="75"/>
-      <c r="P13" s="81"/>
-      <c r="Q13" s="81"/>
-      <c r="R13" s="81"/>
-      <c r="S13" s="75"/>
-      <c r="T13" s="75"/>
-      <c r="U13" s="81"/>
-      <c r="V13" s="81"/>
-    </row>
-    <row r="14" spans="1:24" s="93" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A14" s="84" t="s">
-        <v>73</v>
-      </c>
-      <c r="B14" s="85"/>
-      <c r="C14" s="86"/>
-      <c r="D14" s="87" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" s="88" t="s">
-        <v>72</v>
-      </c>
-      <c r="F14" s="87" t="s">
-        <v>34</v>
-      </c>
-      <c r="G14" s="89" t="s">
-        <v>74</v>
-      </c>
-      <c r="H14" s="90"/>
-      <c r="I14" s="87" t="s">
-        <v>69</v>
-      </c>
-      <c r="J14" s="84" t="s">
+      <c r="G15" s="71" t="s">
         <v>67</v>
       </c>
-      <c r="K14" s="91"/>
-      <c r="L14" s="85"/>
-      <c r="M14" s="86"/>
-      <c r="N14" s="84" t="s">
-        <v>36</v>
-      </c>
-      <c r="O14" s="85"/>
-      <c r="P14" s="92"/>
-      <c r="Q14" s="84" t="s">
-        <v>37</v>
-      </c>
-      <c r="R14" s="85"/>
-      <c r="S14" s="84" t="s">
+      <c r="H15" s="69"/>
+      <c r="I15" s="75" t="s">
+        <v>59</v>
+      </c>
+      <c r="J15" s="71" t="s">
         <v>66</v>
       </c>
-      <c r="T14" s="91"/>
-      <c r="U14" s="84" t="s">
-        <v>70</v>
-      </c>
-      <c r="V14" s="92"/>
-      <c r="X14" s="86"/>
-    </row>
-    <row r="15" spans="1:24" s="74" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="76" t="s">
-        <v>58</v>
-      </c>
-      <c r="B15" s="77"/>
-      <c r="C15" s="78"/>
-      <c r="D15" s="79" t="s">
-        <v>59</v>
-      </c>
-      <c r="E15" s="80" t="s">
-        <v>76</v>
-      </c>
-      <c r="F15" s="95" t="s">
-        <v>75</v>
-      </c>
-      <c r="G15" s="80" t="s">
-        <v>78</v>
-      </c>
-      <c r="H15" s="78"/>
-      <c r="I15" s="94" t="s">
+      <c r="K15" s="68"/>
+      <c r="L15" s="68"/>
+      <c r="M15" s="69"/>
+      <c r="N15" s="71" t="s">
         <v>60</v>
       </c>
-      <c r="J15" s="80" t="s">
-        <v>77</v>
-      </c>
-      <c r="K15" s="77"/>
-      <c r="L15" s="77"/>
-      <c r="M15" s="78"/>
-      <c r="N15" s="80" t="s">
+      <c r="O15" s="68"/>
+      <c r="P15" s="69"/>
+      <c r="Q15" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="O15" s="77"/>
-      <c r="P15" s="78"/>
-      <c r="Q15" s="76" t="s">
-        <v>64</v>
-      </c>
-      <c r="R15" s="77"/>
-      <c r="S15" s="83" t="s">
+      <c r="R15" s="68"/>
+      <c r="S15" s="72" t="s">
+        <v>62</v>
+      </c>
+      <c r="T15" s="68"/>
+      <c r="U15" s="73" t="s">
         <v>63</v>
       </c>
-      <c r="T15" s="77"/>
-      <c r="U15" s="82" t="s">
-        <v>62</v>
-      </c>
-      <c r="V15" s="78"/>
-      <c r="X15" s="78"/>
-    </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="107" t="s">
-        <v>48</v>
-      </c>
-      <c r="G16" s="24"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="108" t="s">
-        <v>49</v>
-      </c>
-      <c r="K16" s="108"/>
-      <c r="L16" s="14"/>
-      <c r="N16" s="16"/>
-      <c r="P16" s="14"/>
-      <c r="Q16" s="114" t="s">
-        <v>50</v>
-      </c>
-      <c r="R16" s="114"/>
-      <c r="S16" s="47"/>
-      <c r="T16" s="14"/>
-      <c r="U16" s="12"/>
-      <c r="V16" s="16"/>
-      <c r="W16" s="14"/>
-      <c r="X16" s="14" t="s">
-        <v>0</v>
-      </c>
+      <c r="V15" s="69"/>
+      <c r="X15" s="69"/>
+    </row>
+    <row r="16" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F16" s="1"/>
+      <c r="U16" s="7"/>
     </row>
     <row r="17" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
-      <c r="B17" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="41" t="s">
-        <v>91</v>
-      </c>
-      <c r="D17" s="17"/>
-      <c r="E17" s="107"/>
-      <c r="F17" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="108"/>
-      <c r="K17" s="108"/>
-      <c r="L17" s="41" t="s">
-        <v>88</v>
-      </c>
-      <c r="M17" s="17"/>
-      <c r="N17" s="17"/>
-      <c r="O17" s="17"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="114"/>
-      <c r="R17" s="114"/>
-      <c r="S17" s="41" t="s">
-        <v>89</v>
-      </c>
-      <c r="T17" s="19"/>
-      <c r="U17" s="17"/>
-      <c r="V17" s="51"/>
+      <c r="B17" s="77" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" s="78" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" s="79"/>
+      <c r="F17" s="78" t="s">
+        <v>78</v>
+      </c>
+      <c r="G17" s="79"/>
+      <c r="H17" s="79"/>
+      <c r="I17" s="79"/>
+      <c r="L17" s="78" t="s">
+        <v>79</v>
+      </c>
+      <c r="M17" s="79"/>
+      <c r="N17" s="79"/>
+      <c r="O17" s="79"/>
+      <c r="P17" s="80"/>
+      <c r="S17" s="78" t="s">
+        <v>80</v>
+      </c>
+      <c r="T17" s="80"/>
+      <c r="U17" s="79"/>
+      <c r="V17" s="15"/>
       <c r="W17"/>
     </row>
-    <row r="18" spans="1:24" s="20" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A18" s="21"/>
-      <c r="B18" s="33"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="37"/>
-      <c r="I18" s="21"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="37"/>
-      <c r="M18" s="37"/>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="37"/>
-      <c r="Q18" s="21"/>
-      <c r="S18" s="37"/>
-      <c r="T18" s="37"/>
-      <c r="U18" s="37"/>
-      <c r="V18" s="98"/>
+    <row r="18" spans="1:24" s="83" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
+      <c r="A18" s="81"/>
+      <c r="B18" s="82"/>
+      <c r="D18" s="84"/>
+      <c r="E18" s="85"/>
+      <c r="F18" s="86"/>
+      <c r="G18" s="84"/>
+      <c r="I18" s="81"/>
+      <c r="K18" s="85"/>
+      <c r="L18" s="84"/>
+      <c r="M18" s="84"/>
+      <c r="N18" s="84"/>
+      <c r="O18" s="84"/>
+      <c r="P18" s="84"/>
+      <c r="Q18" s="81"/>
+      <c r="S18" s="84"/>
+      <c r="T18" s="84"/>
+      <c r="U18" s="84"/>
+      <c r="V18" s="90"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
-      <c r="B19" s="31"/>
+      <c r="B19" s="87"/>
       <c r="D19" s="1"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="14"/>
+      <c r="E19" s="88"/>
+      <c r="F19" s="89"/>
       <c r="I19" s="1"/>
-      <c r="J19" s="108" t="s">
-        <v>53</v>
-      </c>
-      <c r="K19" s="108"/>
+      <c r="J19" s="98" t="s">
+        <v>69</v>
+      </c>
+      <c r="K19" s="98"/>
       <c r="M19"/>
       <c r="N19" s="1"/>
-      <c r="O19" s="12"/>
-      <c r="Q19" s="108" t="s">
-        <v>92</v>
-      </c>
-      <c r="R19" s="108"/>
+      <c r="O19" s="7"/>
+      <c r="Q19" s="98" t="s">
+        <v>86</v>
+      </c>
+      <c r="R19" s="98"/>
       <c r="S19" s="1"/>
       <c r="T19"/>
-      <c r="V19" s="12"/>
+      <c r="V19" s="7"/>
       <c r="X19"/>
     </row>
     <row r="20" spans="1:24" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
-      <c r="B20" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="41" t="s">
-        <v>84</v>
+      <c r="B20" s="77" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="78" t="s">
+        <v>81</v>
       </c>
       <c r="D20" s="17"/>
-      <c r="E20" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="F20" s="41" t="s">
-        <v>85</v>
+      <c r="E20" s="77" t="s">
+        <v>71</v>
+      </c>
+      <c r="F20" s="78" t="s">
+        <v>82</v>
       </c>
       <c r="G20" s="17"/>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
-      <c r="J20" s="108"/>
-      <c r="K20" s="108"/>
-      <c r="L20" s="41" t="s">
-        <v>86</v>
-      </c>
-      <c r="M20" s="19"/>
+      <c r="J20" s="98"/>
+      <c r="K20" s="98"/>
+      <c r="L20" s="78" t="s">
+        <v>83</v>
+      </c>
+      <c r="M20" s="91"/>
       <c r="N20" s="17"/>
       <c r="O20" s="17"/>
       <c r="P20" s="17"/>
-      <c r="Q20" s="108"/>
-      <c r="R20" s="108"/>
-      <c r="S20" s="41" t="s">
-        <v>93</v>
-      </c>
-      <c r="T20" s="19"/>
+      <c r="Q20" s="98"/>
+      <c r="R20" s="98"/>
+      <c r="S20" s="78" t="s">
+        <v>87</v>
+      </c>
+      <c r="T20" s="91"/>
       <c r="U20" s="17"/>
       <c r="V20" s="17"/>
       <c r="X20"/>
     </row>
-    <row r="21" spans="1:24" s="20" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="21"/>
-      <c r="B21" s="33"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="37"/>
-      <c r="I21" s="21"/>
-      <c r="K21" s="18"/>
-      <c r="L21" s="37"/>
-      <c r="M21" s="37"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="37"/>
-      <c r="P21" s="37"/>
-      <c r="Q21" s="21"/>
-      <c r="V21" s="98"/>
+    <row r="21" spans="1:24" s="83" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="81"/>
+      <c r="B21" s="82"/>
+      <c r="E21" s="85"/>
+      <c r="F21" s="111"/>
+      <c r="I21" s="81"/>
+      <c r="K21" s="85"/>
+      <c r="Q21" s="81"/>
+      <c r="V21" s="90"/>
     </row>
     <row r="22" spans="1:24" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="1"/>
-      <c r="B22" s="31"/>
+      <c r="A22" s="112" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="112"/>
       <c r="D22" s="1"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="14"/>
+      <c r="E22" s="88"/>
+      <c r="F22" s="89"/>
       <c r="I22" s="1"/>
       <c r="J22"/>
-      <c r="K22" s="32"/>
+      <c r="K22" s="11"/>
       <c r="M22"/>
       <c r="N22" s="1"/>
-      <c r="O22" s="12"/>
+      <c r="O22" s="7"/>
+      <c r="Q22" s="112" t="s">
+        <v>88</v>
+      </c>
+      <c r="R22" s="112"/>
+      <c r="S22" s="1"/>
       <c r="T22"/>
-      <c r="U22"/>
-      <c r="V22" s="97"/>
+      <c r="V22" s="7"/>
       <c r="W22"/>
       <c r="X22"/>
     </row>
     <row r="23" spans="1:24" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="1"/>
-      <c r="B23" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23" s="41" t="s">
-        <v>90</v>
+      <c r="A23" s="112"/>
+      <c r="B23" s="112"/>
+      <c r="C23" s="78" t="s">
+        <v>84</v>
       </c>
       <c r="D23" s="17"/>
-      <c r="E23" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="F23" s="41" t="s">
-        <v>94</v>
+      <c r="E23" s="77" t="s">
+        <v>73</v>
+      </c>
+      <c r="F23" s="78" t="s">
+        <v>89</v>
       </c>
       <c r="G23" s="17"/>
       <c r="H23" s="17"/>
@@ -2545,124 +2567,91 @@
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" s="17"/>
-      <c r="O23" s="122"/>
-      <c r="P23" s="122"/>
-      <c r="Q23" s="122"/>
-      <c r="R23" s="122"/>
-      <c r="S23" s="123"/>
-      <c r="T23" s="123"/>
-      <c r="U23" s="123"/>
-      <c r="V23" s="124"/>
+      <c r="O23" s="17"/>
+      <c r="Q23" s="112"/>
+      <c r="R23" s="112"/>
+      <c r="S23" s="78" t="s">
+        <v>90</v>
+      </c>
+      <c r="T23" s="91"/>
+      <c r="U23" s="17"/>
+      <c r="V23" s="17"/>
       <c r="W23"/>
       <c r="X23"/>
     </row>
-    <row r="24" spans="1:24" s="20" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="B24" s="21"/>
-      <c r="D24" s="37"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="34"/>
-      <c r="J24" s="34"/>
-      <c r="K24" s="34"/>
-      <c r="L24" s="21"/>
-      <c r="M24" s="37"/>
-      <c r="N24" s="37"/>
-      <c r="O24" s="37"/>
-      <c r="P24" s="37"/>
-      <c r="R24" s="21"/>
-      <c r="S24" s="21"/>
-      <c r="V24" s="98"/>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="F24" s="1"/>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="E25" s="1"/>
       <c r="F25" s="1"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="1"/>
-      <c r="M25"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="1"/>
-      <c r="R25"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="12"/>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.2">
       <c r="F26" s="1"/>
-      <c r="U26" s="12"/>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.2">
       <c r="F27" s="1"/>
-      <c r="U27" s="12"/>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.2">
       <c r="F28" s="1"/>
-      <c r="U28" s="12"/>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.2">
       <c r="F29" s="1"/>
-      <c r="U29" s="12"/>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.2">
       <c r="F30" s="1"/>
-      <c r="U30" s="12"/>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.2">
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
       <c r="F31" s="1"/>
-      <c r="U31" s="12"/>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.2">
       <c r="F32" s="1"/>
-      <c r="U32" s="12"/>
-    </row>
-    <row r="33" spans="6:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F33" s="1"/>
-      <c r="U33" s="12"/>
-    </row>
-    <row r="34" spans="6:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F34" s="1"/>
     </row>
-    <row r="35" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="35" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F35" s="1"/>
     </row>
-    <row r="36" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="36" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F36" s="1"/>
     </row>
-    <row r="37" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F37" s="1"/>
     </row>
-    <row r="38" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F38" s="1"/>
     </row>
-    <row r="39" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F39" s="1"/>
     </row>
-    <row r="40" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="40" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F40" s="1"/>
     </row>
-    <row r="41" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="41" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F41" s="1"/>
     </row>
-    <row r="42" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F42" s="1"/>
     </row>
-    <row r="43" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="43" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F43" s="1"/>
     </row>
-    <row r="44" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F44" s="1"/>
     </row>
-    <row r="45" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="45" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F45" s="1"/>
     </row>
-    <row r="46" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F46" s="1"/>
     </row>
-    <row r="47" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F47" s="1"/>
     </row>
-    <row r="48" spans="6:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F48" s="1"/>
     </row>
     <row r="49" spans="6:6" x14ac:dyDescent="0.2">
@@ -2824,120 +2813,45 @@
     <row r="101" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F101" s="1"/>
     </row>
-    <row r="102" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F102" s="1"/>
-    </row>
-    <row r="103" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F103" s="1"/>
-    </row>
-    <row r="104" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F104" s="1"/>
-    </row>
-    <row r="105" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F105" s="1"/>
-    </row>
-    <row r="106" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F106" s="1"/>
-    </row>
-    <row r="107" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F107" s="1"/>
-    </row>
-    <row r="108" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F108" s="1"/>
-    </row>
-    <row r="109" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F109" s="1"/>
-    </row>
-    <row r="110" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F110" s="1"/>
-    </row>
-    <row r="111" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F111" s="1"/>
-    </row>
-    <row r="112" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F112" s="1"/>
-    </row>
-    <row r="113" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F113" s="1"/>
-    </row>
-    <row r="114" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F114" s="1"/>
-    </row>
-    <row r="115" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F115" s="1"/>
-    </row>
-    <row r="116" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F116" s="1"/>
-    </row>
-    <row r="117" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F117" s="1"/>
-    </row>
-    <row r="118" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F118" s="1"/>
-    </row>
-    <row r="119" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F119" s="1"/>
-    </row>
-    <row r="120" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F120" s="1"/>
-    </row>
-    <row r="121" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F121" s="1"/>
-    </row>
-    <row r="122" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F122" s="1"/>
-    </row>
-    <row r="123" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F123" s="1"/>
-    </row>
-    <row r="124" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F124" s="1"/>
-    </row>
-    <row r="125" spans="6:6" x14ac:dyDescent="0.2">
-      <c r="F125" s="1"/>
-    </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <mergeCells count="15">
-    <mergeCell ref="K1:V1"/>
+  <mergeCells count="18">
     <mergeCell ref="J19:K20"/>
-    <mergeCell ref="T6:T7"/>
-    <mergeCell ref="S6:S7"/>
-    <mergeCell ref="Q16:R17"/>
-    <mergeCell ref="K6:M6"/>
-    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="Q19:R20"/>
+    <mergeCell ref="A22:B23"/>
+    <mergeCell ref="Q22:R23"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:M6"/>
+    <mergeCell ref="N6:R6"/>
+    <mergeCell ref="H1:V1"/>
     <mergeCell ref="U6:V7"/>
     <mergeCell ref="U10:V10"/>
-    <mergeCell ref="Q19:R20"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="K3:O3"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="J16:K17"/>
+    <mergeCell ref="S6:T6"/>
   </mergeCells>
-  <conditionalFormatting sqref="C8:D8">
-    <cfRule type="expression" dxfId="2" priority="7" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D10:E10">
-    <cfRule type="expression" dxfId="1" priority="11" stopIfTrue="1">
+  <conditionalFormatting sqref="D8">
+    <cfRule type="expression" dxfId="1" priority="8" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D11:F13">
-    <cfRule type="expression" dxfId="0" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation showErrorMessage="1" sqref="K4 F23 C20 C17 S17 L17 F17 F20 C23 L20 S20" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="H10" xr:uid="{00000000-0002-0000-0000-000001000000}"/>
-    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="G16 H11:H13" xr:uid="{00000000-0002-0000-0000-000002000000}">
+  <dataValidations count="3">
+    <dataValidation showErrorMessage="1" sqref="H4 F23 C20 C17 S17 L17 F17 F20 C23 L20 S20 S23" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="F10 H11:H13" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I8" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I8" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
@@ -2946,8 +2860,8 @@
     <hyperlink ref="A3" r:id="rId1" display="www.federation.org" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="A4" r:id="rId2" display="records@federation.org" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
-  <pageMargins left="0.31496062992125984" right="0.35433070866141736" top="0.39370078740157483" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.31496062992125984"/>
-  <pageSetup scale="67" firstPageNumber="0" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId3"/>
+  <pageMargins left="0.31496062992125984" right="0.35433070866141736" top="0.39370078740157483" bottom="0.47244094488188981" header="0.51181102362204722" footer="0.23622047244094491"/>
+  <pageSetup scale="57" firstPageNumber="0" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId3"/>
   <headerFooter alignWithMargins="0"/>
   <legacyDrawing r:id="rId4"/>
 </worksheet>

--- a/owlcms/src/main/resources/templates/protocol/SnCJTot-LETTER.xlsx
+++ b/owlcms/src/main/resources/templates/protocol/SnCJTot-LETTER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms4\owlcms\src\main\resources\templates\protocol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{779383C6-C623-4FF1-9EDA-646DE922C775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B84862D3-D0AF-4A9F-B87D-C3A0105DE3F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="11505" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -156,7 +156,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="100">
   <si>
     <t>${l.lotNumber}</t>
   </si>
@@ -429,18 +429,47 @@
   </si>
   <si>
     <t>${session.reserveJuryAsTO} ${session.reserveJuryAsTO.federationId}</t>
+  </si>
+  <si>
+    <t>${t.get("Marshall")}</t>
+  </si>
+  <si>
+    <t>${session.marshallAsTO} ${session.marshallAsTO.federation}
+${session.marshal2AsTO} ${session.marshal2AsTO.federation}</t>
+  </si>
+  <si>
+    <t>${t.get("Timekeeper")}</t>
+  </si>
+  <si>
+    <t>${t.get("Results.Controller")}</t>
+  </si>
+  <si>
+    <t>${session.technicalControllerAsTO} ${session.technicalControllerAsTO.federation}
+${session.technicalController2AsTO} ${session.technicalController2AsTO.federation}</t>
+  </si>
+  <si>
+    <t>${t.get("Doctor")}</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>${session.timeKeeperAsTO} ${session.timeKeeperAsTO.federation}</t>
+  </si>
+  <si>
+    <t>${session.doctorAsTO} ${session.doctorAsTO.federation}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" ns1:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_-#,##0;[Red]\(#,##0\);\-"/>
     <numFmt numFmtId="165" formatCode="0;\(0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.000;;\-"/>
   </numFmts>
-  <fonts count="35" x14ac:knownFonts="1">
+  <fonts count="50" ns2:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -655,8 +684,91 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="30">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -740,8 +852,53 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
   </fills>
-  <borders count="30">
+  <borders count="45">
     <border>
       <left/>
       <right/>
@@ -1097,6 +1254,121 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color indexed="8"/>
       </bottom>
@@ -1124,7 +1396,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1448,6 +1720,47 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="15" borderId="30" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="16" borderId="31" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="17" borderId="32" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="18" borderId="33" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="19" borderId="34" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="40" fillId="20" borderId="35" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="21" borderId="36" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="42" fillId="22" borderId="37" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="43" fillId="23" borderId="38" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="24" borderId="39" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="25" borderId="40" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="26" borderId="41" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="27" borderId="42" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="28" borderId="43" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="29" borderId="44" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Accent1" xfId="1" builtinId="29" customBuiltin="1"/>
@@ -1456,18 +1769,18 @@
     <cellStyle name="Accent4" xfId="4" builtinId="41" customBuiltin="1"/>
     <cellStyle name="Accent5" xfId="5" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Accent6" xfId="6" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Emphase 1" xfId="7" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Emphase 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Emphase 3" xfId="9" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Emphase 1" xfId="7" ns3:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Emphase 2" xfId="8" ns3:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Emphase 3" xfId="9" ns3:uid="{00000000-0005-0000-0000-000008000000}"/>
     <cellStyle name="Hyperlink" xfId="10" builtinId="8"/>
-    <cellStyle name="Lien hypertexte 2" xfId="11" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Lien hypertexte 2" xfId="11" ns3:uid="{00000000-0005-0000-0000-00000A000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="12" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="Normal 3" xfId="13" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="Titre 1" xfId="14" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="Titre 1 1" xfId="15" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="Titre 1 1 1" xfId="16" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="Titre de la feuille" xfId="17" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Normal 2" xfId="12" ns3:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Normal 3" xfId="13" ns3:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Titre 1" xfId="14" ns3:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Titre 1 1" xfId="15" ns3:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Titre 1 1 1" xfId="16" ns3:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Titre de la feuille" xfId="17" ns3:uid="{00000000-0005-0000-0000-000011000000}"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="2">
@@ -1558,11 +1871,11 @@
     </indexedColors>
   </colors>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <ns4:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <ns5:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1915,12 +2228,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Feuil4">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X101"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" ns3:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="1"/>
     <col min="2" max="2" width="5.42578125" style="1" customWidth="1"/>
@@ -1944,7 +2257,7 @@
     <col min="25" max="25" width="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>19</v>
       </c>
@@ -1974,7 +2287,7 @@
       <c r="U1" s="116"/>
       <c r="V1" s="116"/>
     </row>
-    <row r="2" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" ht="19.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A2" s="18" t="s">
         <v>20</v>
       </c>
@@ -2002,7 +2315,7 @@
       <c r="R2" s="115"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="19.5" customHeight="1" ns3:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>21</v>
       </c>
@@ -2032,7 +2345,7 @@
       <c r="U3" s="29"/>
       <c r="V3" s="29"/>
     </row>
-    <row r="4" spans="1:24" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" ht="19.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A4" s="24" t="s">
         <v>23</v>
       </c>
@@ -2052,8 +2365,8 @@
       <c r="P4" s="30"/>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" spans="1:24" ht="6" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="6" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" ht="6" customHeight="1" ns3:dyDescent="0.2"/>
+    <row r="6" spans="1:24" ht="15" customHeight="1" ns3:dyDescent="0.2">
       <c r="A6" s="105" t="s">
         <v>38</v>
       </c>
@@ -2102,7 +2415,7 @@
       <c r="V6" s="93"/>
       <c r="X6"/>
     </row>
-    <row r="7" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.2">
       <c r="A7" s="106"/>
       <c r="B7" s="106"/>
       <c r="C7" s="108"/>
@@ -2150,7 +2463,7 @@
       <c r="U7" s="94"/>
       <c r="V7" s="95"/>
     </row>
-    <row r="8" spans="1:24" s="10" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" s="10" customFormat="1" ht="7.5" customHeight="1" ns3:dyDescent="0.2">
       <c r="A8" s="32"/>
       <c r="B8" s="32"/>
       <c r="C8" s="32"/>
@@ -2163,7 +2476,7 @@
       <c r="J8" s="33"/>
       <c r="K8" s="34"/>
     </row>
-    <row r="9" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" ht="21.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A9" s="35" t="s">
         <v>47</v>
       </c>
@@ -2190,7 +2503,7 @@
       <c r="V9" s="38"/>
       <c r="X9"/>
     </row>
-    <row r="10" spans="1:24" s="10" customFormat="1" ht="21.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" s="10" customFormat="1" ht="21.2" customHeight="1" ns3:dyDescent="0.2">
       <c r="A10" s="8" t="s">
         <v>1</v>
       </c>
@@ -2256,7 +2569,7 @@
       </c>
       <c r="V10" s="97"/>
     </row>
-    <row r="11" spans="1:24" ht="24.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" ht="24.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="B11"/>
       <c r="G11"/>
       <c r="H11"/>
@@ -2274,13 +2587,13 @@
       <c r="W11"/>
       <c r="X11"/>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="15" ns3:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J12" s="14"/>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="6.75" customHeight="1" ns3:dyDescent="0.25">
       <c r="A13" s="55"/>
       <c r="B13" s="55"/>
       <c r="C13" s="55"/>
@@ -2304,7 +2617,7 @@
       <c r="U13" s="56"/>
       <c r="V13" s="56"/>
     </row>
-    <row r="14" spans="1:24" s="66" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" s="66" customFormat="1" ht="12" ns3:dyDescent="0.2">
       <c r="A14" s="57" t="s">
         <v>49</v>
       </c>
@@ -2351,7 +2664,7 @@
       <c r="V14" s="65"/>
       <c r="X14" s="59"/>
     </row>
-    <row r="15" spans="1:24" s="74" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" s="74" customFormat="1" ns3:dyDescent="0.2">
       <c r="A15" s="67" t="s">
         <v>57</v>
       </c>
@@ -2398,61 +2711,80 @@
       <c r="V15" s="69"/>
       <c r="X15" s="69"/>
     </row>
-    <row r="16" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F16" s="1"/>
-      <c r="U16" s="7"/>
-    </row>
-    <row r="17" spans="1:24" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1"/>
-      <c r="B17" s="77" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="78" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" s="79"/>
-      <c r="F17" s="78" t="s">
-        <v>78</v>
-      </c>
-      <c r="G17" s="79"/>
-      <c r="H17" s="79"/>
-      <c r="I17" s="79"/>
-      <c r="L17" s="78" t="s">
-        <v>79</v>
-      </c>
-      <c r="M17" s="79"/>
-      <c r="N17" s="79"/>
-      <c r="O17" s="79"/>
-      <c r="P17" s="80"/>
-      <c r="S17" s="78" t="s">
-        <v>80</v>
-      </c>
-      <c r="T17" s="80"/>
-      <c r="U17" s="79"/>
-      <c r="V17" s="15"/>
-      <c r="W17"/>
-    </row>
-    <row r="18" spans="1:24" s="83" customFormat="1" ht="11.25" x14ac:dyDescent="0.2">
-      <c r="A18" s="81"/>
-      <c r="B18" s="82"/>
-      <c r="D18" s="84"/>
-      <c r="E18" s="85"/>
-      <c r="F18" s="86"/>
-      <c r="G18" s="84"/>
-      <c r="I18" s="81"/>
-      <c r="K18" s="85"/>
-      <c r="L18" s="84"/>
-      <c r="M18" s="84"/>
-      <c r="N18" s="84"/>
-      <c r="O18" s="84"/>
-      <c r="P18" s="84"/>
-      <c r="Q18" s="81"/>
-      <c r="S18" s="84"/>
-      <c r="T18" s="84"/>
-      <c r="U18" s="84"/>
-      <c r="V18" s="90"/>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" ht="6" customHeight="1" ns3:dyDescent="0.2">
+      <c r="C16" s="117"/>
+      <c r="D16" s="117"/>
+    </row>
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="20.25" customHeight="1" ns3:dyDescent="0.2">
+      <c r="A17" s="118" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="118"/>
+      <c r="C17" s="119" t="s">
+        <v>92</v>
+      </c>
+      <c r="D17" s="119"/>
+      <c r="E17" s="118" t="s">
+        <v>93</v>
+      </c>
+      <c r="F17" s="120"/>
+      <c r="G17" s="121"/>
+      <c r="H17" s="122"/>
+      <c r="I17" s="123"/>
+      <c r="J17" s="118" t="s">
+        <v>94</v>
+      </c>
+      <c r="K17" s="118"/>
+      <c r="L17" s="119" t="s">
+        <v>95</v>
+      </c>
+      <c r="M17" s="119"/>
+      <c r="N17" s="119"/>
+      <c r="O17" s="119"/>
+      <c r="P17" s="119"/>
+      <c r="Q17" s="124" t="s">
+        <v>96</v>
+      </c>
+      <c r="R17" s="124"/>
+      <c r="S17" s="121"/>
+      <c r="T17" s="122"/>
+      <c r="U17" s="123"/>
+      <c r="V17" s="125"/>
+      <c r="W17" s="126"/>
+      <c r="X17" s="126" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" ht="16.5" customHeight="1" ns3:dyDescent="0.2">
+      <c r="A18" s="118"/>
+      <c r="B18" s="118"/>
+      <c r="C18" s="127"/>
+      <c r="D18" s="127"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="128" t="s">
+        <v>98</v>
+      </c>
+      <c r="G18" s="129"/>
+      <c r="H18" s="130"/>
+      <c r="I18" s="131"/>
+      <c r="J18" s="118"/>
+      <c r="K18" s="118"/>
+      <c r="L18" s="127"/>
+      <c r="M18" s="127"/>
+      <c r="N18" s="127"/>
+      <c r="O18" s="127"/>
+      <c r="P18" s="127"/>
+      <c r="Q18" s="124"/>
+      <c r="R18" s="124"/>
+      <c r="S18" s="128" t="s">
+        <v>99</v>
+      </c>
+      <c r="T18" s="130"/>
+      <c r="U18" s="131"/>
+      <c r="V18" s="131"/>
+      <c r="W18"/>
+    </row>
+    <row r="19" spans="1:24" ns3:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="87"/>
       <c r="D19" s="1"/>
@@ -2475,7 +2807,7 @@
       <c r="V19" s="7"/>
       <c r="X19"/>
     </row>
-    <row r="20" spans="1:24" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:24" ht="13.7" customHeight="1" ns3:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="77" t="s">
         <v>70</v>
@@ -2512,7 +2844,7 @@
       <c r="V20" s="17"/>
       <c r="X20"/>
     </row>
-    <row r="21" spans="1:24" s="83" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:24" s="83" customFormat="1" ht="12.75" customHeight="1" ns3:dyDescent="0.2">
       <c r="A21" s="81"/>
       <c r="B21" s="82"/>
       <c r="E21" s="85"/>
@@ -2522,7 +2854,7 @@
       <c r="Q21" s="81"/>
       <c r="V21" s="90"/>
     </row>
-    <row r="22" spans="1:24" ht="17.45" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:24" ht="17.45" customHeight="1" ns3:dyDescent="0.2">
       <c r="A22" s="112" t="s">
         <v>72</v>
       </c>
@@ -2546,7 +2878,7 @@
       <c r="W22"/>
       <c r="X22"/>
     </row>
-    <row r="23" spans="1:24" ht="13.7" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:24" ht="13.7" customHeight="1" ns3:dyDescent="0.2">
       <c r="A23" s="112"/>
       <c r="B23" s="112"/>
       <c r="C23" s="78" t="s">
@@ -2579,243 +2911,243 @@
       <c r="W23"/>
       <c r="X23"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:24" ns3:dyDescent="0.2">
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:24" ns3:dyDescent="0.2">
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:24" ns3:dyDescent="0.2">
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:24" ns3:dyDescent="0.2">
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:24" ns3:dyDescent="0.2">
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:24" ns3:dyDescent="0.2">
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:24" ns3:dyDescent="0.2">
       <c r="F30" s="1"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:24" ns3:dyDescent="0.2">
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:24" ns3:dyDescent="0.2">
       <c r="F32" s="1"/>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="6:6" ns3:dyDescent="0.2">
       <c r="F33" s="1"/>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="6:6" ns3:dyDescent="0.2">
       <c r="F34" s="1"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="6:6" ns3:dyDescent="0.2">
       <c r="F35" s="1"/>
     </row>
-    <row r="36" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="36" spans="6:6" ns3:dyDescent="0.2">
       <c r="F36" s="1"/>
     </row>
-    <row r="37" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="6:6" ns3:dyDescent="0.2">
       <c r="F37" s="1"/>
     </row>
-    <row r="38" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="6:6" ns3:dyDescent="0.2">
       <c r="F38" s="1"/>
     </row>
-    <row r="39" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="39" spans="6:6" ns3:dyDescent="0.2">
       <c r="F39" s="1"/>
     </row>
-    <row r="40" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="6:6" ns3:dyDescent="0.2">
       <c r="F40" s="1"/>
     </row>
-    <row r="41" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="6:6" ns3:dyDescent="0.2">
       <c r="F41" s="1"/>
     </row>
-    <row r="42" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="42" spans="6:6" ns3:dyDescent="0.2">
       <c r="F42" s="1"/>
     </row>
-    <row r="43" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="6:6" ns3:dyDescent="0.2">
       <c r="F43" s="1"/>
     </row>
-    <row r="44" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="6:6" ns3:dyDescent="0.2">
       <c r="F44" s="1"/>
     </row>
-    <row r="45" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="6:6" ns3:dyDescent="0.2">
       <c r="F45" s="1"/>
     </row>
-    <row r="46" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="6:6" ns3:dyDescent="0.2">
       <c r="F46" s="1"/>
     </row>
-    <row r="47" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="47" spans="6:6" ns3:dyDescent="0.2">
       <c r="F47" s="1"/>
     </row>
-    <row r="48" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="6:6" ns3:dyDescent="0.2">
       <c r="F48" s="1"/>
     </row>
-    <row r="49" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="6:6" ns3:dyDescent="0.2">
       <c r="F49" s="1"/>
     </row>
-    <row r="50" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="6:6" ns3:dyDescent="0.2">
       <c r="F50" s="1"/>
     </row>
-    <row r="51" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="6:6" ns3:dyDescent="0.2">
       <c r="F51" s="1"/>
     </row>
-    <row r="52" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="6:6" ns3:dyDescent="0.2">
       <c r="F52" s="1"/>
     </row>
-    <row r="53" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="53" spans="6:6" ns3:dyDescent="0.2">
       <c r="F53" s="1"/>
     </row>
-    <row r="54" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="6:6" ns3:dyDescent="0.2">
       <c r="F54" s="1"/>
     </row>
-    <row r="55" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="55" spans="6:6" ns3:dyDescent="0.2">
       <c r="F55" s="1"/>
     </row>
-    <row r="56" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="56" spans="6:6" ns3:dyDescent="0.2">
       <c r="F56" s="1"/>
     </row>
-    <row r="57" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="57" spans="6:6" ns3:dyDescent="0.2">
       <c r="F57" s="1"/>
     </row>
-    <row r="58" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="58" spans="6:6" ns3:dyDescent="0.2">
       <c r="F58" s="1"/>
     </row>
-    <row r="59" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="59" spans="6:6" ns3:dyDescent="0.2">
       <c r="F59" s="1"/>
     </row>
-    <row r="60" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="60" spans="6:6" ns3:dyDescent="0.2">
       <c r="F60" s="1"/>
     </row>
-    <row r="61" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="6:6" ns3:dyDescent="0.2">
       <c r="F61" s="1"/>
     </row>
-    <row r="62" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="6:6" ns3:dyDescent="0.2">
       <c r="F62" s="1"/>
     </row>
-    <row r="63" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="6:6" ns3:dyDescent="0.2">
       <c r="F63" s="1"/>
     </row>
-    <row r="64" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="64" spans="6:6" ns3:dyDescent="0.2">
       <c r="F64" s="1"/>
     </row>
-    <row r="65" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="6:6" ns3:dyDescent="0.2">
       <c r="F65" s="1"/>
     </row>
-    <row r="66" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="6:6" ns3:dyDescent="0.2">
       <c r="F66" s="1"/>
     </row>
-    <row r="67" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="6:6" ns3:dyDescent="0.2">
       <c r="F67" s="1"/>
     </row>
-    <row r="68" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="6:6" ns3:dyDescent="0.2">
       <c r="F68" s="1"/>
     </row>
-    <row r="69" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="6:6" ns3:dyDescent="0.2">
       <c r="F69" s="1"/>
     </row>
-    <row r="70" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="70" spans="6:6" ns3:dyDescent="0.2">
       <c r="F70" s="1"/>
     </row>
-    <row r="71" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="71" spans="6:6" ns3:dyDescent="0.2">
       <c r="F71" s="1"/>
     </row>
-    <row r="72" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="6:6" ns3:dyDescent="0.2">
       <c r="F72" s="1"/>
     </row>
-    <row r="73" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="6:6" ns3:dyDescent="0.2">
       <c r="F73" s="1"/>
     </row>
-    <row r="74" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="74" spans="6:6" ns3:dyDescent="0.2">
       <c r="F74" s="1"/>
     </row>
-    <row r="75" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="75" spans="6:6" ns3:dyDescent="0.2">
       <c r="F75" s="1"/>
     </row>
-    <row r="76" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="76" spans="6:6" ns3:dyDescent="0.2">
       <c r="F76" s="1"/>
     </row>
-    <row r="77" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="77" spans="6:6" ns3:dyDescent="0.2">
       <c r="F77" s="1"/>
     </row>
-    <row r="78" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="78" spans="6:6" ns3:dyDescent="0.2">
       <c r="F78" s="1"/>
     </row>
-    <row r="79" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="6:6" ns3:dyDescent="0.2">
       <c r="F79" s="1"/>
     </row>
-    <row r="80" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="6:6" ns3:dyDescent="0.2">
       <c r="F80" s="1"/>
     </row>
-    <row r="81" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="6:6" ns3:dyDescent="0.2">
       <c r="F81" s="1"/>
     </row>
-    <row r="82" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="82" spans="6:6" ns3:dyDescent="0.2">
       <c r="F82" s="1"/>
     </row>
-    <row r="83" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="6:6" ns3:dyDescent="0.2">
       <c r="F83" s="1"/>
     </row>
-    <row r="84" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="6:6" ns3:dyDescent="0.2">
       <c r="F84" s="1"/>
     </row>
-    <row r="85" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="85" spans="6:6" ns3:dyDescent="0.2">
       <c r="F85" s="1"/>
     </row>
-    <row r="86" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="86" spans="6:6" ns3:dyDescent="0.2">
       <c r="F86" s="1"/>
     </row>
-    <row r="87" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="87" spans="6:6" ns3:dyDescent="0.2">
       <c r="F87" s="1"/>
     </row>
-    <row r="88" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="88" spans="6:6" ns3:dyDescent="0.2">
       <c r="F88" s="1"/>
     </row>
-    <row r="89" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="89" spans="6:6" ns3:dyDescent="0.2">
       <c r="F89" s="1"/>
     </row>
-    <row r="90" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="90" spans="6:6" ns3:dyDescent="0.2">
       <c r="F90" s="1"/>
     </row>
-    <row r="91" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="91" spans="6:6" ns3:dyDescent="0.2">
       <c r="F91" s="1"/>
     </row>
-    <row r="92" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="92" spans="6:6" ns3:dyDescent="0.2">
       <c r="F92" s="1"/>
     </row>
-    <row r="93" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="93" spans="6:6" ns3:dyDescent="0.2">
       <c r="F93" s="1"/>
     </row>
-    <row r="94" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="94" spans="6:6" ns3:dyDescent="0.2">
       <c r="F94" s="1"/>
     </row>
-    <row r="95" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="95" spans="6:6" ns3:dyDescent="0.2">
       <c r="F95" s="1"/>
     </row>
-    <row r="96" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="96" spans="6:6" ns3:dyDescent="0.2">
       <c r="F96" s="1"/>
     </row>
-    <row r="97" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="97" spans="6:6" ns3:dyDescent="0.2">
       <c r="F97" s="1"/>
     </row>
-    <row r="98" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="98" spans="6:6" ns3:dyDescent="0.2">
       <c r="F98" s="1"/>
     </row>
-    <row r="99" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="99" spans="6:6" ns3:dyDescent="0.2">
       <c r="F99" s="1"/>
     </row>
-    <row r="100" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="100" spans="6:6" ns3:dyDescent="0.2">
       <c r="F100" s="1"/>
     </row>
-    <row r="101" spans="6:6" x14ac:dyDescent="0.2">
+    <row r="101" spans="6:6" ns3:dyDescent="0.2">
       <c r="F101" s="1"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <mergeCells count="18">
+  <mergeCells count="24">
     <mergeCell ref="J19:K20"/>
     <mergeCell ref="Q19:R20"/>
     <mergeCell ref="A22:B23"/>
@@ -2834,6 +3166,12 @@
     <mergeCell ref="U6:V7"/>
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="S6:T6"/>
+    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="C17:D18"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="L17:P18"/>
+    <mergeCell ref="J17:K18"/>
+    <mergeCell ref="Q17:R18"/>
   </mergeCells>
   <conditionalFormatting sqref="D8">
     <cfRule type="expression" dxfId="1" priority="8" stopIfTrue="1">
@@ -2846,23 +3184,23 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation showErrorMessage="1" sqref="H4 F23 C20 C17 S17 L17 F17 F20 C23 L20 S20 S23" xr:uid="{00000000-0002-0000-0000-000000000000}"/>
-    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="F10 H11:H13" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation showErrorMessage="1" sqref="H4 F23 C20 C17 S17 L17 F17 F20 C23 L20 S20 S23" ns2:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="F10 H11:H13" ns2:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I8" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I8" ns2:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A3" r:id="rId1" display="www.federation.org" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="A4" r:id="rId2" display="records@federation.org" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A3" ns4:id="rId1" display="www.federation.org" ns2:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A4" ns4:id="rId2" display="records@federation.org" ns2:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.31496062992125984" right="0.35433070866141736" top="0.39370078740157483" bottom="0.47244094488188981" header="0.51181102362204722" footer="0.23622047244094491"/>
-  <pageSetup scale="57" firstPageNumber="0" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId3"/>
+  <pageSetup scale="57" firstPageNumber="0" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" ns4:id="rId3"/>
   <headerFooter alignWithMargins="0"/>
-  <legacyDrawing r:id="rId4"/>
+  <legacyDrawing ns4:id="rId4"/>
 </worksheet>
 </file>
--- a/owlcms/src/main/resources/templates/protocol/SnCJTot-LETTER.xlsx
+++ b/owlcms/src/main/resources/templates/protocol/SnCJTot-LETTER.xlsx
@@ -463,7 +463,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" ns1:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_-#,##0;[Red]\(#,##0\);\-"/>
     <numFmt numFmtId="165" formatCode="0;\(0\);\-"/>
@@ -2228,7 +2228,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns2:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Feuil4">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/owlcms/src/main/resources/templates/protocol/SnCJTot-LETTER.xlsx
+++ b/owlcms/src/main/resources/templates/protocol/SnCJTot-LETTER.xlsx
@@ -123,7 +123,7 @@
             <rFont val="Tahoma"/>
             <charset val="1"/>
           </rPr>
-          <t>jx:if(condition="records != null" lastCell="V15")</t>
+          <t>jx:if(condition="session.records.size() &gt; 0" lastCell="V15")</t>
         </r>
       </text>
     </comment>
@@ -147,7 +147,7 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-jx:each(items="records" var="r" lastCell="V15")</t>
+jx:each(items="session.records" var="r" lastCell="V15")</t>
         </r>
       </text>
     </comment>
@@ -463,13 +463,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_-#,##0;[Red]\(#,##0\);\-"/>
     <numFmt numFmtId="165" formatCode="0;\(0\);\-"/>
     <numFmt numFmtId="166" formatCode="0.000;;\-"/>
   </numFmts>
-  <fonts count="50" ns2:knownFonts="1">
+  <fonts count="142" ns1:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -766,6 +766,571 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
     </font>
   </fonts>
   <fills count="30">
@@ -898,7 +1463,7 @@
       <patternFill patternType="none"/>
     </fill>
   </fills>
-  <borders count="45">
+  <borders count="135">
     <border>
       <left/>
       <right/>
@@ -1373,6 +1938,660 @@
         <color indexed="8"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <diagonal/>
+      <bottom/>
     </border>
   </borders>
   <cellStyleXfs count="19">
@@ -1396,7 +2615,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="233">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1761,6 +2980,328 @@
     <xf numFmtId="0" fontId="49" fillId="29" borderId="44" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="45" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="46" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="47" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="48" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="49" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="50" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="51" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="52" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="53" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="57" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="58" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="59" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="60" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="61" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="62" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="63" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="64" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="65" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="71" fillId="0" borderId="66" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1" applyAlignment="1">
+      <protection locked="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="72" fillId="0" borderId="67" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1" applyAlignment="1">
+      <protection locked="0"/>
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="73" fillId="0" borderId="68" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1" applyAlignment="1">
+      <protection locked="0"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="77" fillId="0" borderId="72" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="78" fillId="0" borderId="73" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="79" fillId="0" borderId="74" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="78" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="79" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="80" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="81" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="82" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="83" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="84" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="85" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="90" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="91" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="92" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="93" xfId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="94" xfId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="95" xfId="10" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="96" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="97" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="98" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="104" fillId="0" borderId="99" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="105" fillId="0" borderId="100" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="106" fillId="0" borderId="101" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="102" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="103" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="104" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="105" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="106" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="112" fillId="0" borderId="107" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="113" fillId="0" borderId="108" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="114" fillId="0" borderId="109" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="115" fillId="0" borderId="110" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="116" fillId="0" borderId="111" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="112" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="118" fillId="0" borderId="113" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="119" fillId="0" borderId="114" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="120" fillId="0" borderId="115" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="116" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="122" fillId="0" borderId="117" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="123" fillId="0" borderId="118" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="0" borderId="119" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="125" fillId="0" borderId="120" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="126" fillId="0" borderId="121" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="127" fillId="0" borderId="122" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="128" fillId="0" borderId="123" xfId="0" applyProtection="1" applyAlignment="1">
+      <protection locked="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="129" fillId="0" borderId="124" xfId="0" applyProtection="1" applyAlignment="1">
+      <protection locked="0"/>
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="130" fillId="0" borderId="125" xfId="0" applyProtection="1" applyAlignment="1">
+      <protection locked="0"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="131" fillId="0" borderId="126" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="132" fillId="0" borderId="127" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="133" fillId="0" borderId="128" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="134" fillId="0" borderId="129" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="135" fillId="0" borderId="130" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="136" fillId="0" borderId="131" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="137" fillId="0" borderId="132" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="138" fillId="0" borderId="133" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="139" fillId="0" borderId="134" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="78" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyBorder="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="105" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="106" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="117" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="121" fillId="0" borderId="0" xfId="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="140" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="141" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="0" applyAlignment="1" applyProtection="1" applyFont="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="19">
     <cellStyle name="Accent1" xfId="1" builtinId="29" customBuiltin="1"/>
@@ -1769,18 +3310,18 @@
     <cellStyle name="Accent4" xfId="4" builtinId="41" customBuiltin="1"/>
     <cellStyle name="Accent5" xfId="5" builtinId="45" customBuiltin="1"/>
     <cellStyle name="Accent6" xfId="6" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Emphase 1" xfId="7" ns3:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Emphase 2" xfId="8" ns3:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="Emphase 3" xfId="9" ns3:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Emphase 1" xfId="7" ns2:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Emphase 2" xfId="8" ns2:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Emphase 3" xfId="9" ns2:uid="{00000000-0005-0000-0000-000008000000}"/>
     <cellStyle name="Hyperlink" xfId="10" builtinId="8"/>
-    <cellStyle name="Lien hypertexte 2" xfId="11" ns3:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Lien hypertexte 2" xfId="11" ns2:uid="{00000000-0005-0000-0000-00000A000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="12" ns3:uid="{00000000-0005-0000-0000-00000C000000}"/>
-    <cellStyle name="Normal 3" xfId="13" ns3:uid="{00000000-0005-0000-0000-00000D000000}"/>
-    <cellStyle name="Titre 1" xfId="14" ns3:uid="{00000000-0005-0000-0000-00000E000000}"/>
-    <cellStyle name="Titre 1 1" xfId="15" ns3:uid="{00000000-0005-0000-0000-00000F000000}"/>
-    <cellStyle name="Titre 1 1 1" xfId="16" ns3:uid="{00000000-0005-0000-0000-000010000000}"/>
-    <cellStyle name="Titre de la feuille" xfId="17" ns3:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Normal 2" xfId="12" ns2:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="Normal 3" xfId="13" ns2:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="Titre 1" xfId="14" ns2:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="Titre 1 1" xfId="15" ns2:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="Titre 1 1 1" xfId="16" ns2:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="Titre de la feuille" xfId="17" ns2:uid="{00000000-0005-0000-0000-000011000000}"/>
     <cellStyle name="Total" xfId="18" builtinId="25" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="2">
@@ -1872,10 +3413,10 @@
   </colors>
   <extLst>
     <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <ns4:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+      <ns3:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
     <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <ns5:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+      <ns4:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2228,12 +3769,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns4="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Feuil4">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:X101"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" ns3:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" ns2:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.85546875" customWidth="1"/>
     <col min="2" max="2" width="5.42578125" style="1" customWidth="1"/>
@@ -2257,116 +3798,71 @@
     <col min="25" max="25" width="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15.75" customHeight="1" ns3:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="116" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" s="116"/>
-      <c r="J1" s="116"/>
-      <c r="K1" s="116"/>
-      <c r="L1" s="116"/>
-      <c r="M1" s="116"/>
-      <c r="N1" s="116"/>
-      <c r="O1" s="116"/>
-      <c r="P1" s="116"/>
-      <c r="Q1" s="116"/>
-      <c r="R1" s="116"/>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
-      <c r="V1" s="116"/>
-    </row>
-    <row r="2" spans="1:24" ht="19.5" customHeight="1" ns3:dyDescent="0.2">
-      <c r="A2" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="4"/>
-      <c r="G2" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="113"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" s="114" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q2" s="115"/>
-      <c r="R2" s="115"/>
-      <c r="S2" s="1"/>
-    </row>
-    <row r="3" spans="1:24" ht="19.5" customHeight="1" ns3:dyDescent="0.25">
-      <c r="A3" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="25"/>
-      <c r="G3" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29"/>
-      <c r="V3" s="29"/>
-    </row>
-    <row r="4" spans="1:24" ht="19.5" customHeight="1" ns3:dyDescent="0.2">
-      <c r="A4" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="24"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="G4" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="H4" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="I4"/>
-      <c r="J4" s="3"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="30"/>
-      <c r="S4" s="1"/>
-    </row>
-    <row r="5" spans="1:24" ht="6" customHeight="1" ns3:dyDescent="0.2"/>
-    <row r="6" spans="1:24" ht="15" customHeight="1" ns3:dyDescent="0.2">
+    <row r="1" spans="1:24" ht="24" customHeight="1" ns2:dyDescent="0.25">
+      <c r="A1" s="222" t="inlineStr">
+        <is>
+          <t>${competition.competitionName}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" spans="1:24" ht="24" customHeight="1" ns2:dyDescent="0.2">
+      <c r="A2" s="223" t="inlineStr">
+        <is>
+          <t>${t.get("Competition.competitionSite")} :</t>
+        </is>
+      </c>
+      <c r="D2" s="224" t="inlineStr">
+        <is>
+          <t>${competition.competitionSite}</t>
+        </is>
+      </c>
+      <c r="K2" s="225" t="inlineStr">
+        <is>
+          <t>${t.get("Competition.competitionCity")} :</t>
+        </is>
+      </c>
+      <c r="N2" s="226" t="inlineStr">
+        <is>
+          <t>${competition.competitionCity}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" spans="1:24" ht="24" customHeight="1" ns2:dyDescent="0.25">
+      <c r="A3" s="227" t="inlineStr">
+        <is>
+          <t>${t.get("Competition.competitionDate")} :</t>
+        </is>
+      </c>
+      <c r="D3" s="228" t="inlineStr">
+        <is>
+          <t>${competition.localizedCompetitionDate}</t>
+        </is>
+      </c>
+      <c r="K3" s="231" t="inlineStr">
+        <is>
+          <t>${t.get("Competition.competitionOrganizer")} :</t>
+        </is>
+      </c>
+      <c r="N3" s="230" t="inlineStr">
+        <is>
+          <t>${competition.competitionOrganizer}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" spans="1:24" ht="19.5" customHeight="1" ns2:dyDescent="0.2">
+      <c r="A4" s="232" t="inlineStr">
+        <is>
+          <t>${session != null ? t.get("Group") + " :" : ""}</t>
+        </is>
+      </c>
+      <c r="D4" s="228" t="inlineStr">
+        <is>
+          <t>${session != null ? session.name : ""}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="6" customHeight="1" ns2:dyDescent="0.2"/>
+    <row r="6" spans="1:24" ht="15" customHeight="1" ns2:dyDescent="0.2">
       <c r="A6" s="105" t="s">
         <v>38</v>
       </c>
@@ -2415,7 +3911,7 @@
       <c r="V6" s="93"/>
       <c r="X6"/>
     </row>
-    <row r="7" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" ns3:dyDescent="0.2">
+    <row r="7" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" ns2:dyDescent="0.2">
       <c r="A7" s="106"/>
       <c r="B7" s="106"/>
       <c r="C7" s="108"/>
@@ -2463,7 +3959,7 @@
       <c r="U7" s="94"/>
       <c r="V7" s="95"/>
     </row>
-    <row r="8" spans="1:24" s="10" customFormat="1" ht="7.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="8" spans="1:24" s="10" customFormat="1" ht="7.5" customHeight="1" ns2:dyDescent="0.2">
       <c r="A8" s="32"/>
       <c r="B8" s="32"/>
       <c r="C8" s="32"/>
@@ -2476,7 +3972,7 @@
       <c r="J8" s="33"/>
       <c r="K8" s="34"/>
     </row>
-    <row r="9" spans="1:24" ht="21.75" customHeight="1" ns3:dyDescent="0.2">
+    <row r="9" spans="1:24" ht="21.75" customHeight="1" ns2:dyDescent="0.2">
       <c r="A9" s="35" t="s">
         <v>47</v>
       </c>
@@ -2503,7 +3999,7 @@
       <c r="V9" s="38"/>
       <c r="X9"/>
     </row>
-    <row r="10" spans="1:24" s="10" customFormat="1" ht="21.2" customHeight="1" ns3:dyDescent="0.2">
+    <row r="10" spans="1:24" s="10" customFormat="1" ht="21.2" customHeight="1" ns2:dyDescent="0.2">
       <c r="A10" s="8" t="s">
         <v>1</v>
       </c>
@@ -2569,7 +4065,7 @@
       </c>
       <c r="V10" s="97"/>
     </row>
-    <row r="11" spans="1:24" ht="24.75" customHeight="1" ns3:dyDescent="0.2">
+    <row r="11" spans="1:24" ht="24.75" customHeight="1" ns2:dyDescent="0.2">
       <c r="B11"/>
       <c r="G11"/>
       <c r="H11"/>
@@ -2587,13 +4083,13 @@
       <c r="W11"/>
       <c r="X11"/>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="15" ns3:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="15" ns2:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>48</v>
       </c>
       <c r="J12" s="14"/>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="6.75" customHeight="1" ns3:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="6.75" customHeight="1" ns2:dyDescent="0.25">
       <c r="A13" s="55"/>
       <c r="B13" s="55"/>
       <c r="C13" s="55"/>
@@ -2617,7 +4113,7 @@
       <c r="U13" s="56"/>
       <c r="V13" s="56"/>
     </row>
-    <row r="14" spans="1:24" s="66" customFormat="1" ht="12" ns3:dyDescent="0.2">
+    <row r="14" spans="1:24" s="66" customFormat="1" ht="12" ns2:dyDescent="0.2">
       <c r="A14" s="57" t="s">
         <v>49</v>
       </c>
@@ -2664,7 +4160,7 @@
       <c r="V14" s="65"/>
       <c r="X14" s="59"/>
     </row>
-    <row r="15" spans="1:24" s="74" customFormat="1" ns3:dyDescent="0.2">
+    <row r="15" spans="1:24" s="74" customFormat="1" ns2:dyDescent="0.2">
       <c r="A15" s="67" t="s">
         <v>57</v>
       </c>
@@ -2711,11 +4207,11 @@
       <c r="V15" s="69"/>
       <c r="X15" s="69"/>
     </row>
-    <row r="16" spans="1:24" ht="6" customHeight="1" ns3:dyDescent="0.2">
+    <row r="16" spans="1:24" ht="6" customHeight="1" ns2:dyDescent="0.2">
       <c r="C16" s="117"/>
       <c r="D16" s="117"/>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="20.25" customHeight="1" ns3:dyDescent="0.2">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="20.25" customHeight="1" ns2:dyDescent="0.2">
       <c r="A17" s="118" t="s">
         <v>91</v>
       </c>
@@ -2755,7 +4251,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="16.5" customHeight="1" ns3:dyDescent="0.2">
+    <row r="18" spans="1:24" ht="16.5" customHeight="1" ns2:dyDescent="0.2">
       <c r="A18" s="118"/>
       <c r="B18" s="118"/>
       <c r="C18" s="127"/>
@@ -2784,7 +4280,7 @@
       <c r="V18" s="131"/>
       <c r="W18"/>
     </row>
-    <row r="19" spans="1:24" ns3:dyDescent="0.2">
+    <row r="19" spans="1:24" ns2:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="87"/>
       <c r="D19" s="1"/>
@@ -2807,7 +4303,7 @@
       <c r="V19" s="7"/>
       <c r="X19"/>
     </row>
-    <row r="20" spans="1:24" ht="13.7" customHeight="1" ns3:dyDescent="0.2">
+    <row r="20" spans="1:24" ht="13.7" customHeight="1" ns2:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="77" t="s">
         <v>70</v>
@@ -2844,7 +4340,7 @@
       <c r="V20" s="17"/>
       <c r="X20"/>
     </row>
-    <row r="21" spans="1:24" s="83" customFormat="1" ht="12.75" customHeight="1" ns3:dyDescent="0.2">
+    <row r="21" spans="1:24" s="83" customFormat="1" ht="12.75" customHeight="1" ns2:dyDescent="0.2">
       <c r="A21" s="81"/>
       <c r="B21" s="82"/>
       <c r="E21" s="85"/>
@@ -2854,7 +4350,7 @@
       <c r="Q21" s="81"/>
       <c r="V21" s="90"/>
     </row>
-    <row r="22" spans="1:24" ht="17.45" customHeight="1" ns3:dyDescent="0.2">
+    <row r="22" spans="1:24" ht="17.45" customHeight="1" ns2:dyDescent="0.2">
       <c r="A22" s="112" t="s">
         <v>72</v>
       </c>
@@ -2878,7 +4374,7 @@
       <c r="W22"/>
       <c r="X22"/>
     </row>
-    <row r="23" spans="1:24" ht="13.7" customHeight="1" ns3:dyDescent="0.2">
+    <row r="23" spans="1:24" ht="13.7" customHeight="1" ns2:dyDescent="0.2">
       <c r="A23" s="112"/>
       <c r="B23" s="112"/>
       <c r="C23" s="78" t="s">
@@ -2911,243 +4407,243 @@
       <c r="W23"/>
       <c r="X23"/>
     </row>
-    <row r="24" spans="1:24" ns3:dyDescent="0.2">
+    <row r="24" spans="1:24" ns2:dyDescent="0.2">
       <c r="F24" s="1"/>
     </row>
-    <row r="25" spans="1:24" ns3:dyDescent="0.2">
+    <row r="25" spans="1:24" ns2:dyDescent="0.2">
       <c r="F25" s="1"/>
     </row>
-    <row r="26" spans="1:24" ns3:dyDescent="0.2">
+    <row r="26" spans="1:24" ns2:dyDescent="0.2">
       <c r="F26" s="1"/>
     </row>
-    <row r="27" spans="1:24" ns3:dyDescent="0.2">
+    <row r="27" spans="1:24" ns2:dyDescent="0.2">
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="1:24" ns3:dyDescent="0.2">
+    <row r="28" spans="1:24" ns2:dyDescent="0.2">
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="1:24" ns3:dyDescent="0.2">
+    <row r="29" spans="1:24" ns2:dyDescent="0.2">
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="1:24" ns3:dyDescent="0.2">
+    <row r="30" spans="1:24" ns2:dyDescent="0.2">
       <c r="F30" s="1"/>
     </row>
-    <row r="31" spans="1:24" ns3:dyDescent="0.2">
+    <row r="31" spans="1:24" ns2:dyDescent="0.2">
       <c r="F31" s="1"/>
     </row>
-    <row r="32" spans="1:24" ns3:dyDescent="0.2">
+    <row r="32" spans="1:24" ns2:dyDescent="0.2">
       <c r="F32" s="1"/>
     </row>
-    <row r="33" spans="6:6" ns3:dyDescent="0.2">
+    <row r="33" spans="6:6" ns2:dyDescent="0.2">
       <c r="F33" s="1"/>
     </row>
-    <row r="34" spans="6:6" ns3:dyDescent="0.2">
+    <row r="34" spans="6:6" ns2:dyDescent="0.2">
       <c r="F34" s="1"/>
     </row>
-    <row r="35" spans="6:6" ns3:dyDescent="0.2">
+    <row r="35" spans="6:6" ns2:dyDescent="0.2">
       <c r="F35" s="1"/>
     </row>
-    <row r="36" spans="6:6" ns3:dyDescent="0.2">
+    <row r="36" spans="6:6" ns2:dyDescent="0.2">
       <c r="F36" s="1"/>
     </row>
-    <row r="37" spans="6:6" ns3:dyDescent="0.2">
+    <row r="37" spans="6:6" ns2:dyDescent="0.2">
       <c r="F37" s="1"/>
     </row>
-    <row r="38" spans="6:6" ns3:dyDescent="0.2">
+    <row r="38" spans="6:6" ns2:dyDescent="0.2">
       <c r="F38" s="1"/>
     </row>
-    <row r="39" spans="6:6" ns3:dyDescent="0.2">
+    <row r="39" spans="6:6" ns2:dyDescent="0.2">
       <c r="F39" s="1"/>
     </row>
-    <row r="40" spans="6:6" ns3:dyDescent="0.2">
+    <row r="40" spans="6:6" ns2:dyDescent="0.2">
       <c r="F40" s="1"/>
     </row>
-    <row r="41" spans="6:6" ns3:dyDescent="0.2">
+    <row r="41" spans="6:6" ns2:dyDescent="0.2">
       <c r="F41" s="1"/>
     </row>
-    <row r="42" spans="6:6" ns3:dyDescent="0.2">
+    <row r="42" spans="6:6" ns2:dyDescent="0.2">
       <c r="F42" s="1"/>
     </row>
-    <row r="43" spans="6:6" ns3:dyDescent="0.2">
+    <row r="43" spans="6:6" ns2:dyDescent="0.2">
       <c r="F43" s="1"/>
     </row>
-    <row r="44" spans="6:6" ns3:dyDescent="0.2">
+    <row r="44" spans="6:6" ns2:dyDescent="0.2">
       <c r="F44" s="1"/>
     </row>
-    <row r="45" spans="6:6" ns3:dyDescent="0.2">
+    <row r="45" spans="6:6" ns2:dyDescent="0.2">
       <c r="F45" s="1"/>
     </row>
-    <row r="46" spans="6:6" ns3:dyDescent="0.2">
+    <row r="46" spans="6:6" ns2:dyDescent="0.2">
       <c r="F46" s="1"/>
     </row>
-    <row r="47" spans="6:6" ns3:dyDescent="0.2">
+    <row r="47" spans="6:6" ns2:dyDescent="0.2">
       <c r="F47" s="1"/>
     </row>
-    <row r="48" spans="6:6" ns3:dyDescent="0.2">
+    <row r="48" spans="6:6" ns2:dyDescent="0.2">
       <c r="F48" s="1"/>
     </row>
-    <row r="49" spans="6:6" ns3:dyDescent="0.2">
+    <row r="49" spans="6:6" ns2:dyDescent="0.2">
       <c r="F49" s="1"/>
     </row>
-    <row r="50" spans="6:6" ns3:dyDescent="0.2">
+    <row r="50" spans="6:6" ns2:dyDescent="0.2">
       <c r="F50" s="1"/>
     </row>
-    <row r="51" spans="6:6" ns3:dyDescent="0.2">
+    <row r="51" spans="6:6" ns2:dyDescent="0.2">
       <c r="F51" s="1"/>
     </row>
-    <row r="52" spans="6:6" ns3:dyDescent="0.2">
+    <row r="52" spans="6:6" ns2:dyDescent="0.2">
       <c r="F52" s="1"/>
     </row>
-    <row r="53" spans="6:6" ns3:dyDescent="0.2">
+    <row r="53" spans="6:6" ns2:dyDescent="0.2">
       <c r="F53" s="1"/>
     </row>
-    <row r="54" spans="6:6" ns3:dyDescent="0.2">
+    <row r="54" spans="6:6" ns2:dyDescent="0.2">
       <c r="F54" s="1"/>
     </row>
-    <row r="55" spans="6:6" ns3:dyDescent="0.2">
+    <row r="55" spans="6:6" ns2:dyDescent="0.2">
       <c r="F55" s="1"/>
     </row>
-    <row r="56" spans="6:6" ns3:dyDescent="0.2">
+    <row r="56" spans="6:6" ns2:dyDescent="0.2">
       <c r="F56" s="1"/>
     </row>
-    <row r="57" spans="6:6" ns3:dyDescent="0.2">
+    <row r="57" spans="6:6" ns2:dyDescent="0.2">
       <c r="F57" s="1"/>
     </row>
-    <row r="58" spans="6:6" ns3:dyDescent="0.2">
+    <row r="58" spans="6:6" ns2:dyDescent="0.2">
       <c r="F58" s="1"/>
     </row>
-    <row r="59" spans="6:6" ns3:dyDescent="0.2">
+    <row r="59" spans="6:6" ns2:dyDescent="0.2">
       <c r="F59" s="1"/>
     </row>
-    <row r="60" spans="6:6" ns3:dyDescent="0.2">
+    <row r="60" spans="6:6" ns2:dyDescent="0.2">
       <c r="F60" s="1"/>
     </row>
-    <row r="61" spans="6:6" ns3:dyDescent="0.2">
+    <row r="61" spans="6:6" ns2:dyDescent="0.2">
       <c r="F61" s="1"/>
     </row>
-    <row r="62" spans="6:6" ns3:dyDescent="0.2">
+    <row r="62" spans="6:6" ns2:dyDescent="0.2">
       <c r="F62" s="1"/>
     </row>
-    <row r="63" spans="6:6" ns3:dyDescent="0.2">
+    <row r="63" spans="6:6" ns2:dyDescent="0.2">
       <c r="F63" s="1"/>
     </row>
-    <row r="64" spans="6:6" ns3:dyDescent="0.2">
+    <row r="64" spans="6:6" ns2:dyDescent="0.2">
       <c r="F64" s="1"/>
     </row>
-    <row r="65" spans="6:6" ns3:dyDescent="0.2">
+    <row r="65" spans="6:6" ns2:dyDescent="0.2">
       <c r="F65" s="1"/>
     </row>
-    <row r="66" spans="6:6" ns3:dyDescent="0.2">
+    <row r="66" spans="6:6" ns2:dyDescent="0.2">
       <c r="F66" s="1"/>
     </row>
-    <row r="67" spans="6:6" ns3:dyDescent="0.2">
+    <row r="67" spans="6:6" ns2:dyDescent="0.2">
       <c r="F67" s="1"/>
     </row>
-    <row r="68" spans="6:6" ns3:dyDescent="0.2">
+    <row r="68" spans="6:6" ns2:dyDescent="0.2">
       <c r="F68" s="1"/>
     </row>
-    <row r="69" spans="6:6" ns3:dyDescent="0.2">
+    <row r="69" spans="6:6" ns2:dyDescent="0.2">
       <c r="F69" s="1"/>
     </row>
-    <row r="70" spans="6:6" ns3:dyDescent="0.2">
+    <row r="70" spans="6:6" ns2:dyDescent="0.2">
       <c r="F70" s="1"/>
     </row>
-    <row r="71" spans="6:6" ns3:dyDescent="0.2">
+    <row r="71" spans="6:6" ns2:dyDescent="0.2">
       <c r="F71" s="1"/>
     </row>
-    <row r="72" spans="6:6" ns3:dyDescent="0.2">
+    <row r="72" spans="6:6" ns2:dyDescent="0.2">
       <c r="F72" s="1"/>
     </row>
-    <row r="73" spans="6:6" ns3:dyDescent="0.2">
+    <row r="73" spans="6:6" ns2:dyDescent="0.2">
       <c r="F73" s="1"/>
     </row>
-    <row r="74" spans="6:6" ns3:dyDescent="0.2">
+    <row r="74" spans="6:6" ns2:dyDescent="0.2">
       <c r="F74" s="1"/>
     </row>
-    <row r="75" spans="6:6" ns3:dyDescent="0.2">
+    <row r="75" spans="6:6" ns2:dyDescent="0.2">
       <c r="F75" s="1"/>
     </row>
-    <row r="76" spans="6:6" ns3:dyDescent="0.2">
+    <row r="76" spans="6:6" ns2:dyDescent="0.2">
       <c r="F76" s="1"/>
     </row>
-    <row r="77" spans="6:6" ns3:dyDescent="0.2">
+    <row r="77" spans="6:6" ns2:dyDescent="0.2">
       <c r="F77" s="1"/>
     </row>
-    <row r="78" spans="6:6" ns3:dyDescent="0.2">
+    <row r="78" spans="6:6" ns2:dyDescent="0.2">
       <c r="F78" s="1"/>
     </row>
-    <row r="79" spans="6:6" ns3:dyDescent="0.2">
+    <row r="79" spans="6:6" ns2:dyDescent="0.2">
       <c r="F79" s="1"/>
     </row>
-    <row r="80" spans="6:6" ns3:dyDescent="0.2">
+    <row r="80" spans="6:6" ns2:dyDescent="0.2">
       <c r="F80" s="1"/>
     </row>
-    <row r="81" spans="6:6" ns3:dyDescent="0.2">
+    <row r="81" spans="6:6" ns2:dyDescent="0.2">
       <c r="F81" s="1"/>
     </row>
-    <row r="82" spans="6:6" ns3:dyDescent="0.2">
+    <row r="82" spans="6:6" ns2:dyDescent="0.2">
       <c r="F82" s="1"/>
     </row>
-    <row r="83" spans="6:6" ns3:dyDescent="0.2">
+    <row r="83" spans="6:6" ns2:dyDescent="0.2">
       <c r="F83" s="1"/>
     </row>
-    <row r="84" spans="6:6" ns3:dyDescent="0.2">
+    <row r="84" spans="6:6" ns2:dyDescent="0.2">
       <c r="F84" s="1"/>
     </row>
-    <row r="85" spans="6:6" ns3:dyDescent="0.2">
+    <row r="85" spans="6:6" ns2:dyDescent="0.2">
       <c r="F85" s="1"/>
     </row>
-    <row r="86" spans="6:6" ns3:dyDescent="0.2">
+    <row r="86" spans="6:6" ns2:dyDescent="0.2">
       <c r="F86" s="1"/>
     </row>
-    <row r="87" spans="6:6" ns3:dyDescent="0.2">
+    <row r="87" spans="6:6" ns2:dyDescent="0.2">
       <c r="F87" s="1"/>
     </row>
-    <row r="88" spans="6:6" ns3:dyDescent="0.2">
+    <row r="88" spans="6:6" ns2:dyDescent="0.2">
       <c r="F88" s="1"/>
     </row>
-    <row r="89" spans="6:6" ns3:dyDescent="0.2">
+    <row r="89" spans="6:6" ns2:dyDescent="0.2">
       <c r="F89" s="1"/>
     </row>
-    <row r="90" spans="6:6" ns3:dyDescent="0.2">
+    <row r="90" spans="6:6" ns2:dyDescent="0.2">
       <c r="F90" s="1"/>
     </row>
-    <row r="91" spans="6:6" ns3:dyDescent="0.2">
+    <row r="91" spans="6:6" ns2:dyDescent="0.2">
       <c r="F91" s="1"/>
     </row>
-    <row r="92" spans="6:6" ns3:dyDescent="0.2">
+    <row r="92" spans="6:6" ns2:dyDescent="0.2">
       <c r="F92" s="1"/>
     </row>
-    <row r="93" spans="6:6" ns3:dyDescent="0.2">
+    <row r="93" spans="6:6" ns2:dyDescent="0.2">
       <c r="F93" s="1"/>
     </row>
-    <row r="94" spans="6:6" ns3:dyDescent="0.2">
+    <row r="94" spans="6:6" ns2:dyDescent="0.2">
       <c r="F94" s="1"/>
     </row>
-    <row r="95" spans="6:6" ns3:dyDescent="0.2">
+    <row r="95" spans="6:6" ns2:dyDescent="0.2">
       <c r="F95" s="1"/>
     </row>
-    <row r="96" spans="6:6" ns3:dyDescent="0.2">
+    <row r="96" spans="6:6" ns2:dyDescent="0.2">
       <c r="F96" s="1"/>
     </row>
-    <row r="97" spans="6:6" ns3:dyDescent="0.2">
+    <row r="97" spans="6:6" ns2:dyDescent="0.2">
       <c r="F97" s="1"/>
     </row>
-    <row r="98" spans="6:6" ns3:dyDescent="0.2">
+    <row r="98" spans="6:6" ns2:dyDescent="0.2">
       <c r="F98" s="1"/>
     </row>
-    <row r="99" spans="6:6" ns3:dyDescent="0.2">
+    <row r="99" spans="6:6" ns2:dyDescent="0.2">
       <c r="F99" s="1"/>
     </row>
-    <row r="100" spans="6:6" ns3:dyDescent="0.2">
+    <row r="100" spans="6:6" ns2:dyDescent="0.2">
       <c r="F100" s="1"/>
     </row>
-    <row r="101" spans="6:6" ns3:dyDescent="0.2">
+    <row r="101" spans="6:6" ns2:dyDescent="0.2">
       <c r="F101" s="1"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <mergeCells count="24">
+  <mergeCells count="34">
     <mergeCell ref="J19:K20"/>
     <mergeCell ref="Q19:R20"/>
     <mergeCell ref="A22:B23"/>
@@ -3162,7 +4658,6 @@
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="I6:M6"/>
     <mergeCell ref="N6:R6"/>
-    <mergeCell ref="H1:V1"/>
     <mergeCell ref="U6:V7"/>
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="S6:T6"/>
@@ -3172,6 +4667,17 @@
     <mergeCell ref="L17:P18"/>
     <mergeCell ref="J17:K18"/>
     <mergeCell ref="Q17:R18"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:V2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="N3:V3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:V4"/>
   </mergeCells>
   <conditionalFormatting sqref="D8">
     <cfRule type="expression" dxfId="1" priority="8" stopIfTrue="1">
@@ -3184,23 +4690,20 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation showErrorMessage="1" sqref="H4 F23 C20 C17 S17 L17 F17 F20 C23 L20 S20 S23" ns2:uid="{00000000-0002-0000-0000-000000000000}"/>
-    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="F10 H11:H13" ns2:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation showErrorMessage="1" sqref="H4 F23 C20 C17 S17 L17 F17 F20 C23 L20 S20 S23" ns1:uid="{00000000-0002-0000-0000-000000000000}"/>
+    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" sqref="F10 H11:H13" ns1:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I8" ns2:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I8" ns1:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>0</formula1>
       <formula2>200</formula2>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="A3" ns4:id="rId1" display="www.federation.org" ns2:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="A4" ns4:id="rId2" display="records@federation.org" ns2:uid="{00000000-0004-0000-0000-000001000000}"/>
-  </hyperlinks>
+  <hyperlinks/>
   <pageMargins left="0.31496062992125984" right="0.35433070866141736" top="0.39370078740157483" bottom="0.47244094488188981" header="0.51181102362204722" footer="0.23622047244094491"/>
-  <pageSetup scale="57" firstPageNumber="0" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" ns4:id="rId3"/>
+  <pageSetup scale="57" firstPageNumber="0" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" ns3:id="rId3"/>
   <headerFooter alignWithMargins="0"/>
-  <legacyDrawing ns4:id="rId4"/>
+  <legacyDrawing ns3:id="rId4"/>
 </worksheet>
 </file>